--- a/AAII_Financials/Quarterly/SOFI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SOFI_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,157 +656,163 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>645200</v>
+      </c>
+      <c r="E8" s="3">
         <v>564300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>470000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>371600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>307400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>198000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>149500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>118400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>94800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>93600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>84100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>82500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>92100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>88100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>86100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>97300</v>
       </c>
-      <c r="S8" s="3">
-        <v>0</v>
-      </c>
       <c r="T8" s="3">
         <v>0</v>
       </c>
       <c r="U8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -864,8 +870,11 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -923,8 +932,11 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -946,8 +958,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1005,8 +1018,11 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1064,8 +1080,11 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1123,8 +1142,11 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1182,8 +1204,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1202,126 +1227,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>267700</v>
+      </c>
+      <c r="E17" s="3">
         <v>241100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>191500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>144000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>113800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>56500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>36900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>36400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>22900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>23600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>28600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>35200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>53300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>38900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>43300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>50100</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>377500</v>
+      </c>
+      <c r="E18" s="3">
         <v>323200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>278500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>227600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>193600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>141500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>112600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>82000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>71900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>70000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>55500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>47300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>38900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>49200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>42800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>47200</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1343,126 +1375,133 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-326400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-590100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-327800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-263700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-232600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-215900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-208300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-191600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-181400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-99800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-220900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-223700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-126400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-91900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-134700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-153500</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>104600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-214400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>9300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-34200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-57700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-78900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-82900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-5800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-140400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-150500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-62100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-18000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-77000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-101600</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1520,126 +1559,135 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>51200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-266900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-49300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-36100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-38900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-74500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-95700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-109600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-109500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-29900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-165400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-176500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-87600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-42700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-92000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-106300</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E24" s="3">
         <v>-200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-4900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-99800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
         <v>0</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1697,126 +1745,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>47900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-266700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-47500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-34400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-40000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-74200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-95800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-110400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-111000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-30000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-165300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-177600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-82600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-42900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>7800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-106400</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>37700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-276900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-57600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-44400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-50200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-84400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-105900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-120300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-121200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-40200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-175400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-187500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-145500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-53100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-116400</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1874,8 +1931,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1933,8 +1993,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1992,8 +2055,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2051,126 +2117,135 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>326400</v>
+      </c>
+      <c r="E32" s="3">
         <v>590100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>327800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>263700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>232600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>215900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>208300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>191600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>181400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>99800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>220900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>223700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>126400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>91900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>134700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>153500</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>37700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-276900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-57600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-44400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-50200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-84400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-105900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-120300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-121200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-40200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-175400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-187500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-145500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-53100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-116400</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2228,131 +2303,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>37700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-276900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-57600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-44400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-50200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-84400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-105900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-120300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-121200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-40200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-175400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-187500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-145500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-53100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-116400</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2374,8 +2458,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2397,47 +2482,48 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3085000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2813900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3015700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2487800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1421900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>935200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>707300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1325100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>494700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>533500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>461900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>351300</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2456,47 +2542,50 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>180500</v>
+      </c>
+      <c r="E42" s="3">
         <v>142700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>145700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>146500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>149900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>168400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>177000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>173500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>168300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>163500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>159800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>161200</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2506,8 +2595,8 @@
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="S42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
@@ -2515,8 +2604,11 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2574,8 +2666,11 @@
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2633,8 +2728,11 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2683,8 +2781,8 @@
       <c r="R45" s="3">
         <v>0</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
+      <c r="S45" s="3">
+        <v>0</v>
       </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
@@ -2692,8 +2790,11 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2742,8 +2843,8 @@
       <c r="R46" s="3">
         <v>0</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
+      <c r="S46" s="3">
+        <v>0</v>
       </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
@@ -2751,19 +2852,22 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
+      <c r="D47" s="3">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3">
+        <v>0</v>
       </c>
       <c r="G47" s="3">
         <v>0</v>
@@ -2778,19 +2882,19 @@
         <v>0</v>
       </c>
       <c r="K47" s="3">
+        <v>0</v>
+      </c>
+      <c r="L47" s="3">
         <v>19700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>20000</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
+      <c r="O47" s="3">
+        <v>0</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
@@ -2810,47 +2914,50 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>306500</v>
+      </c>
+      <c r="E48" s="3">
         <v>295300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>285900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>274400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>267200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>264800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>257500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>243900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>227100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>217000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>208400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>199400</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2860,8 +2967,8 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S48" s="3">
-        <v>0</v>
+      <c r="S48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T48" s="3">
         <v>0</v>
@@ -2869,47 +2976,50 @@
       <c r="U48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1757600</v>
+      </c>
+      <c r="E49" s="3">
         <v>1780800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2052800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2042900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2065100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2079700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2106500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2121200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1183100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1199700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1216300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1235000</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2919,8 +3029,8 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
+      <c r="S49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T49" s="3">
         <v>0</v>
@@ -2928,8 +3038,11 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2987,8 +3100,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3046,8 +3162,11 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3096,8 +3215,8 @@
       <c r="R52" s="3">
         <v>0</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
+      <c r="S52" s="3">
+        <v>0</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
@@ -3105,8 +3224,11 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3164,47 +3286,50 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>30074900</v>
+      </c>
+      <c r="E54" s="3">
         <v>27977200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>25561400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>22453000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>19007700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>15834900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>12670900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>12246600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>9176300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8083300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7653000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7382200</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3223,8 +3348,11 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3246,8 +3374,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3269,47 +3398,48 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>549700</v>
+      </c>
+      <c r="E57" s="3">
         <v>566500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>632500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>554100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>516200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>565900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>542300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>437300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>298200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>325500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>317900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>421100</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3319,8 +3449,8 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S57" s="3">
-        <v>0</v>
+      <c r="S57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T57" s="3">
         <v>0</v>
@@ -3328,8 +3458,11 @@
       <c r="U57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3378,8 +3511,8 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
+      <c r="S58" s="3">
+        <v>0</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
@@ -3387,47 +3520,50 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>108600</v>
+      </c>
+      <c r="E59" s="3">
         <v>113400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>115200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>114900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>117800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>121700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>131700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>136000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>138800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>139900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>135500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>138800</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3446,8 +3582,11 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3496,8 +3635,8 @@
       <c r="R60" s="3">
         <v>0</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
+      <c r="S60" s="3">
+        <v>0</v>
       </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
@@ -3505,47 +3644,50 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5240800</v>
+      </c>
+      <c r="E61" s="3">
         <v>6251600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6495700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6141100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5502900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4614300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3778000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4986700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4041700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2874100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2432500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3942300</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3564,8 +3706,11 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3614,8 +3759,8 @@
       <c r="R62" s="3">
         <v>0</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
+      <c r="S62" s="3">
+        <v>0</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
@@ -3623,8 +3768,11 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3682,8 +3830,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3741,8 +3892,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3800,47 +3954,50 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>24519900</v>
+      </c>
+      <c r="E66" s="3">
         <v>22603400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>19983400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>16898500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>13479200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10333500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7164300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6715900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4478600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3514400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3125200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4502200</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3859,8 +4016,11 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3882,8 +4042,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3941,8 +4102,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4000,8 +4164,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4036,11 +4203,11 @@
         <v>320400</v>
       </c>
       <c r="N70" s="3">
+        <v>320400</v>
+      </c>
+      <c r="O70" s="3">
         <v>3173700</v>
       </c>
-      <c r="O70" s="3">
-        <v>0</v>
-      </c>
       <c r="P70" s="3">
         <v>0</v>
       </c>
@@ -4059,8 +4226,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4118,47 +4288,50 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1804300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1852200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1585500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1537900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1503500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1463500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1389300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1293500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1183100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1072100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1042100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-876700</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4177,8 +4350,11 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4236,8 +4412,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4295,8 +4474,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4354,47 +4536,50 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5234600</v>
+      </c>
+      <c r="E76" s="3">
         <v>5053400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5257700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5234100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5208100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5181000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5186200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5210300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4377300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4248500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4207400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-293600</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4413,8 +4598,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4472,131 +4660,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>37700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-276900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-57600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-44400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-50200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-84400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-105900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-120300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-121200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-40200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-175400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-187500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-145500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-53100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-116400</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4618,67 +4815,71 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>53400</v>
+      </c>
+      <c r="E83" s="3">
         <v>52500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>50100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>45300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>42400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>40300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>38100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>30700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>26500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>24100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>25000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>26000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>25500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>24700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>15000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4700</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
       <c r="T83" s="3">
         <v>0</v>
       </c>
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4736,8 +4937,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4795,8 +4999,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4854,8 +5061,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4913,8 +5123,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4972,67 +5185,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-247900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2686500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2079900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2212800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2418800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2880300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-945500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1011200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1236300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-196500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-257400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>340100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-879400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>122100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>272800</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5054,67 +5273,71 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-36600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-30400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-27600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-26500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-27800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-25900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-24900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-25100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-13800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-11600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-19400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-6900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-8800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-5500</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5172,8 +5395,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5231,67 +5457,73 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1413500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-168500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-267700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-40200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-51400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-50000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-54800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>49900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>30700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-159800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>58400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>180900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>70700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>90800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>32100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>65300</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
         <v>0</v>
       </c>
       <c r="U94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5313,8 +5545,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5372,8 +5605,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5431,8 +5667,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5490,8 +5729,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5549,108 +5791,114 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1979600</v>
+      </c>
+      <c r="E100" s="3">
         <v>2650800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2870800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3384400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3054800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3192500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>297100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1895200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1119700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>441900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>269200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1145800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>462700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>677500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-368300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>81900</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>500</v>
+      </c>
+      <c r="E101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-300</v>
-      </c>
-      <c r="G101" s="3">
-        <v>300</v>
       </c>
       <c r="H101" s="3">
         <v>300</v>
       </c>
       <c r="I101" s="3">
+        <v>300</v>
+      </c>
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="L101" s="3">
         <v>200</v>
       </c>
       <c r="M101" s="3">
+        <v>200</v>
+      </c>
+      <c r="N101" s="3">
         <v>-300</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-100</v>
       </c>
       <c r="O101" s="3">
         <v>-100</v>
       </c>
       <c r="P101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -5667,63 +5915,69 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>318600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-204100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>523600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1131200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>584900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>262500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-703300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>933800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-85800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>85800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>69900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-624900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>538400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-111100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-214100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>420000</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SOFI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SOFI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="92">
   <si>
     <t>SOFI</t>
   </si>
@@ -656,163 +656,170 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>665900</v>
+      </c>
+      <c r="E8" s="3">
         <v>645200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>564300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>470000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>371600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>307400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>198000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>149500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>118400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>94800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>93600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>84100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>82500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>92100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>88100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>86100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>97300</v>
       </c>
-      <c r="T8" s="3">
-        <v>0</v>
-      </c>
       <c r="U8" s="3">
         <v>0</v>
       </c>
       <c r="V8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -873,8 +880,11 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -935,8 +945,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -959,8 +972,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1021,8 +1035,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1083,8 +1100,11 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1145,8 +1165,11 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1207,8 +1230,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1228,132 +1254,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>270400</v>
+      </c>
+      <c r="E17" s="3">
         <v>267700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>241100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>191500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>144000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>113800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>56500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>36900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>36400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>22900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>23600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>28600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>35200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>53300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>38900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>43300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>50100</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>395500</v>
+      </c>
+      <c r="E18" s="3">
         <v>377500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>323200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>278500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>227600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>193600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>141500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>112600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>82000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>71900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>70000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>55500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>47300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>38900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>49200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>42800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>47200</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1376,132 +1409,139 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-301300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-326400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-590100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-327800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-263700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-232600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-215900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-208300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-191600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-181400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-99800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-220900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-223700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-126400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-91900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-134700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-153500</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>142800</v>
+      </c>
+      <c r="E21" s="3">
         <v>104600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-214400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>9300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-34200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-57700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-78900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-82900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-5800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-140400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-150500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-62100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-18000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-77000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-101600</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1562,132 +1602,141 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>94200</v>
+      </c>
+      <c r="E23" s="3">
         <v>51200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-266900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-49300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-36100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-38900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-74500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-95700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-109600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-109500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-29900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-165400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-176500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-87600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-42700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-92000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-106300</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E24" s="3">
         <v>3200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-99800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>100</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
         <v>0</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1748,132 +1797,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>88000</v>
+      </c>
+      <c r="E26" s="3">
         <v>47900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-266700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-47500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-34400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-40000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-74200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-95800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-110400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-111000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-30000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-165300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-177600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-82600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-42900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>7800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-106400</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>78000</v>
+      </c>
+      <c r="E27" s="3">
         <v>37700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-276900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-57600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-44400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-50200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-84400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-105900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-120300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-121200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-40200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-175400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-187500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-145500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-53100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-116400</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1934,8 +1992,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1996,8 +2057,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2058,8 +2122,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2120,132 +2187,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>301300</v>
+      </c>
+      <c r="E32" s="3">
         <v>326400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>590100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>327800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>263700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>232600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>215900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>208300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>191600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>181400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>99800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>220900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>223700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>126400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>91900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>134700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>153500</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>78000</v>
+      </c>
+      <c r="E33" s="3">
         <v>37700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-276900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-57600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-44400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-50200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-84400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-105900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-120300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-121200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-40200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-175400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-187500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-145500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-53100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-116400</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2306,137 +2382,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>78000</v>
+      </c>
+      <c r="E35" s="3">
         <v>37700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-276900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-57600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-44400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-50200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-84400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-105900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-120300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-121200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-40200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-175400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-187500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-145500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-53100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-116400</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2459,8 +2544,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2483,50 +2569,51 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3693400</v>
+      </c>
+      <c r="E41" s="3">
         <v>3085000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2813900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3015700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2487800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1421900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>935200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>707300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1325100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>494700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>533500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>461900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>351300</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2545,50 +2632,53 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>240800</v>
+      </c>
+      <c r="E42" s="3">
         <v>180500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>142700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>145700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>146500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>149900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>168400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>177000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>173500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>168300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>163500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>159800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>161200</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2598,8 +2688,8 @@
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
@@ -2607,8 +2697,11 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2669,8 +2762,11 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2731,8 +2827,11 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2784,8 +2883,8 @@
       <c r="S45" s="3">
         <v>0</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
+      <c r="T45" s="3">
+        <v>0</v>
       </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
@@ -2793,8 +2892,11 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2846,8 +2948,8 @@
       <c r="S46" s="3">
         <v>0</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
+      <c r="T46" s="3">
+        <v>0</v>
       </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
@@ -2855,8 +2957,11 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2885,19 +2990,19 @@
         <v>0</v>
       </c>
       <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3">
         <v>19700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>20000</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
-      </c>
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
+      <c r="P47" s="3">
+        <v>0</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
@@ -2917,50 +3022,53 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>315400</v>
+      </c>
+      <c r="E48" s="3">
         <v>306500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>295300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>285900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>274400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>267200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>264800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>257500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>243900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>227100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>217000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>208400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>199400</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2970,8 +3078,8 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T48" s="3">
-        <v>0</v>
+      <c r="T48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U48" s="3">
         <v>0</v>
@@ -2979,50 +3087,53 @@
       <c r="V48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1741000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1757600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1780800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2052800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2042900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2065100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2079700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2106500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2121200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1183100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1199700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1216300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1235000</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3032,8 +3143,8 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
+      <c r="T49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U49" s="3">
         <v>0</v>
@@ -3041,8 +3152,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3103,8 +3217,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3165,8 +3282,11 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3218,8 +3338,8 @@
       <c r="S52" s="3">
         <v>0</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
+      <c r="T52" s="3">
+        <v>0</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
@@ -3227,8 +3347,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3289,50 +3412,53 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>31305800</v>
+      </c>
+      <c r="E54" s="3">
         <v>30074900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>27977200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>25561400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>22453000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>19007700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>15834900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>12670900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>12246600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>9176300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8083300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7653000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7382200</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3351,8 +3477,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3375,8 +3504,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3399,50 +3529,51 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>554200</v>
+      </c>
+      <c r="E57" s="3">
         <v>549700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>566500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>632500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>554100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>516200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>565900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>542300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>437300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>298200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>325500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>317900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>421100</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3452,8 +3583,8 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T57" s="3">
-        <v>0</v>
+      <c r="T57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U57" s="3">
         <v>0</v>
@@ -3461,8 +3592,11 @@
       <c r="V57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3514,8 +3648,8 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
+      <c r="T58" s="3">
+        <v>0</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
@@ -3523,50 +3657,53 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>105600</v>
+      </c>
+      <c r="E59" s="3">
         <v>108600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>113400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>115200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>114900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>117800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>121700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>131700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>136000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>138800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>139900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>135500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>138800</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3585,8 +3722,11 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3638,8 +3778,8 @@
       <c r="S60" s="3">
         <v>0</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
+      <c r="T60" s="3">
+        <v>0</v>
       </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
@@ -3647,50 +3787,53 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2895400</v>
+      </c>
+      <c r="E61" s="3">
         <v>5240800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6251600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6495700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6141100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5502900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4614300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3778000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4986700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4041700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2874100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2432500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3942300</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3709,8 +3852,11 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3762,8 +3908,8 @@
       <c r="S62" s="3">
         <v>0</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
+      <c r="T62" s="3">
+        <v>0</v>
       </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
@@ -3771,8 +3917,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3833,8 +3982,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3895,8 +4047,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3957,50 +4112,53 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>25159800</v>
+      </c>
+      <c r="E66" s="3">
         <v>24519900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>22603400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>19983400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>16898500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>13479200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10333500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7164300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6715900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4478600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3514400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3125200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4502200</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4019,8 +4177,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4043,8 +4204,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4105,8 +4267,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4167,8 +4332,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4206,11 +4374,11 @@
         <v>320400</v>
       </c>
       <c r="O70" s="3">
+        <v>320400</v>
+      </c>
+      <c r="P70" s="3">
         <v>3173700</v>
       </c>
-      <c r="P70" s="3">
-        <v>0</v>
-      </c>
       <c r="Q70" s="3">
         <v>0</v>
       </c>
@@ -4229,8 +4397,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4291,50 +4462,53 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1716200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1804300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1852200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1585500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1537900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1503500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1463500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1389300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1293500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1183100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1072100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1042100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-876700</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4353,8 +4527,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4415,8 +4592,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4477,8 +4657,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4539,50 +4722,53 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5825600</v>
+      </c>
+      <c r="E76" s="3">
         <v>5234600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5053400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5257700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5234100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5208100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5181000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5186200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5210300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4377300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4248500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4207400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-293600</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4601,8 +4787,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4663,137 +4852,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>78000</v>
+      </c>
+      <c r="E81" s="3">
         <v>37700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-276900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-57600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-44400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-50200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-84400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-105900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-120300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-121200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-40200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-175400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-187500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-145500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-53100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-116400</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4816,70 +5014,74 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>48500</v>
+      </c>
+      <c r="E83" s="3">
         <v>53400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>52500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>50100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>45300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>42400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>40300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>38100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>30700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>26500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>24100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>25000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>26000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>25500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>24700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>15000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4700</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
-      </c>
       <c r="U83" s="3">
         <v>0</v>
       </c>
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4940,8 +5142,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5002,8 +5207,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5064,8 +5272,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5126,8 +5337,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5188,70 +5402,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>738200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-247900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2686500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2079900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2212800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2418800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2880300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-945500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1011200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1236300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-196500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-257400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>340100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>5200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-879400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>122100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>272800</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5274,70 +5494,74 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-34100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-36600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-30400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-27600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-26500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-27800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-25900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-24900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-25100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-13800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-11600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-19400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-7400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-8800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5500</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5398,8 +5622,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5460,70 +5687,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1261200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1413500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-168500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-267700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-40200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-51400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-50000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-54800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>49900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>30700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-159800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>58400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>180900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>70700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>90800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>32100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>65300</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
         <v>0</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5546,8 +5779,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5608,8 +5842,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5670,8 +5907,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5732,8 +5972,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5794,114 +6037,120 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1055400</v>
+      </c>
+      <c r="E100" s="3">
         <v>1979600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2650800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2870800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3384400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3054800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3192500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>297100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1895200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1119700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>441900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>269200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1145800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>462700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>677500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-368300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>81900</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E101" s="3">
         <v>500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-300</v>
-      </c>
-      <c r="H101" s="3">
-        <v>300</v>
       </c>
       <c r="I101" s="3">
         <v>300</v>
       </c>
       <c r="J101" s="3">
+        <v>300</v>
+      </c>
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M101" s="3">
         <v>200</v>
       </c>
       <c r="N101" s="3">
+        <v>200</v>
+      </c>
+      <c r="O101" s="3">
         <v>-300</v>
-      </c>
-      <c r="O101" s="3">
-        <v>-100</v>
       </c>
       <c r="P101" s="3">
         <v>-100</v>
       </c>
       <c r="Q101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -5918,66 +6167,72 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>532300</v>
+      </c>
+      <c r="E102" s="3">
         <v>318600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-204100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>523600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1131200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>584900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>262500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-703300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>933800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-85800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>85800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>69900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-624900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>538400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-111100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-214100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>420000</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SOFI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SOFI_QTR_FIN.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD5FA1F9-2DB2-4C73-9F93-DC8D668FEBC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9345"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SOFI" sheetId="6" r:id="rId1"/>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="92">
   <si>
     <t>SOFI</t>
   </si>
@@ -303,7 +304,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
@@ -369,9 +370,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -409,9 +410,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -446,7 +447,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -481,7 +482,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -654,9 +655,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -675,21 +676,20 @@
     <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
@@ -744,17 +744,8 @@
       <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -809,17 +800,8 @@
       <c r="T8" s="3">
         <v>97300</v>
       </c>
-      <c r="U8" s="3">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3">
-        <v>0</v>
-      </c>
-      <c r="W8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -874,17 +856,8 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -939,17 +912,8 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -970,11 +934,8 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-      <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1029,17 +990,8 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1094,17 +1046,8 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-      <c r="U13" s="3">
-        <v>0</v>
-      </c>
-      <c r="V13" s="3">
-        <v>0</v>
-      </c>
-      <c r="W13" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1159,17 +1102,8 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1224,17 +1158,8 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-      <c r="U15" s="3">
-        <v>0</v>
-      </c>
-      <c r="V15" s="3">
-        <v>0</v>
-      </c>
-      <c r="W15" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1252,11 +1177,8 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-      <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
-      <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1311,17 +1233,8 @@
       <c r="T17" s="3">
         <v>50100</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1376,17 +1289,8 @@
       <c r="T18" s="3">
         <v>47200</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1407,11 +1311,8 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
-      <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1466,17 +1367,8 @@
       <c r="T20" s="3">
         <v>-153500</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1531,17 +1423,8 @@
       <c r="T21" s="3">
         <v>-101600</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1596,17 +1479,8 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
-      </c>
-      <c r="V22" s="3">
-        <v>0</v>
-      </c>
-      <c r="W22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1661,17 +1535,8 @@
       <c r="T23" s="3">
         <v>-106300</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1726,17 +1591,8 @@
       <c r="T24" s="3">
         <v>100</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1791,17 +1647,8 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-      <c r="U25" s="3">
-        <v>0</v>
-      </c>
-      <c r="V25" s="3">
-        <v>0</v>
-      </c>
-      <c r="W25" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1856,17 +1703,8 @@
       <c r="T26" s="3">
         <v>-106400</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1921,17 +1759,8 @@
       <c r="T27" s="3">
         <v>-116400</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1986,17 +1815,8 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-      <c r="U28" s="3">
-        <v>0</v>
-      </c>
-      <c r="V28" s="3">
-        <v>0</v>
-      </c>
-      <c r="W28" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2051,17 +1871,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2116,17 +1927,8 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-      <c r="U30" s="3">
-        <v>0</v>
-      </c>
-      <c r="V30" s="3">
-        <v>0</v>
-      </c>
-      <c r="W30" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2181,17 +1983,8 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-      <c r="U31" s="3">
-        <v>0</v>
-      </c>
-      <c r="V31" s="3">
-        <v>0</v>
-      </c>
-      <c r="W31" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2246,17 +2039,8 @@
       <c r="T32" s="3">
         <v>153500</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2311,17 +2095,8 @@
       <c r="T33" s="3">
         <v>-116400</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2376,17 +2151,8 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-      <c r="U34" s="3">
-        <v>0</v>
-      </c>
-      <c r="V34" s="3">
-        <v>0</v>
-      </c>
-      <c r="W34" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2441,22 +2207,13 @@
       <c r="T35" s="3">
         <v>-116400</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
@@ -2511,17 +2268,8 @@
       <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2542,11 +2290,8 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-      <c r="U39" s="3"/>
-      <c r="V39" s="3"/>
-      <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2567,11 +2312,8 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-      <c r="U40" s="3"/>
-      <c r="V40" s="3"/>
-      <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2626,17 +2368,8 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2691,17 +2424,8 @@
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
-      </c>
-      <c r="V42" s="3">
-        <v>0</v>
-      </c>
-      <c r="W42" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2756,17 +2480,8 @@
       <c r="T43" s="3">
         <v>0</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
-      </c>
-      <c r="V43" s="3">
-        <v>0</v>
-      </c>
-      <c r="W43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2821,17 +2536,8 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-      <c r="U44" s="3">
-        <v>0</v>
-      </c>
-      <c r="V44" s="3">
-        <v>0</v>
-      </c>
-      <c r="W44" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2886,17 +2592,8 @@
       <c r="T45" s="3">
         <v>0</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2951,17 +2648,8 @@
       <c r="T46" s="3">
         <v>0</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3016,17 +2704,8 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3081,17 +2760,8 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
-      </c>
-      <c r="V48" s="3">
-        <v>0</v>
-      </c>
-      <c r="W48" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3146,17 +2816,8 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
-      </c>
-      <c r="V49" s="3">
-        <v>0</v>
-      </c>
-      <c r="W49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3211,17 +2872,8 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-      <c r="U50" s="3">
-        <v>0</v>
-      </c>
-      <c r="V50" s="3">
-        <v>0</v>
-      </c>
-      <c r="W50" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3276,17 +2928,8 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-      <c r="U51" s="3">
-        <v>0</v>
-      </c>
-      <c r="V51" s="3">
-        <v>0</v>
-      </c>
-      <c r="W51" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3341,17 +2984,8 @@
       <c r="T52" s="3">
         <v>0</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3406,17 +3040,8 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-      <c r="U53" s="3">
-        <v>0</v>
-      </c>
-      <c r="V53" s="3">
-        <v>0</v>
-      </c>
-      <c r="W53" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -3471,17 +3096,8 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3502,11 +3118,8 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-      <c r="U55" s="3"/>
-      <c r="V55" s="3"/>
-      <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3527,11 +3140,8 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-      <c r="U56" s="3"/>
-      <c r="V56" s="3"/>
-      <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3586,17 +3196,8 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U57" s="3">
-        <v>0</v>
-      </c>
-      <c r="V57" s="3">
-        <v>0</v>
-      </c>
-      <c r="W57" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3651,17 +3252,8 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3716,17 +3308,8 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3781,17 +3364,8 @@
       <c r="T60" s="3">
         <v>0</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3846,17 +3420,8 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3911,17 +3476,8 @@
       <c r="T62" s="3">
         <v>0</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3976,17 +3532,8 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-      <c r="U63" s="3">
-        <v>0</v>
-      </c>
-      <c r="V63" s="3">
-        <v>0</v>
-      </c>
-      <c r="W63" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4041,17 +3588,8 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-      <c r="U64" s="3">
-        <v>0</v>
-      </c>
-      <c r="V64" s="3">
-        <v>0</v>
-      </c>
-      <c r="W64" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4106,17 +3644,8 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-      <c r="U65" s="3">
-        <v>0</v>
-      </c>
-      <c r="V65" s="3">
-        <v>0</v>
-      </c>
-      <c r="W65" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -4171,17 +3700,8 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4202,11 +3722,8 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-      <c r="U67" s="3"/>
-      <c r="V67" s="3"/>
-      <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4261,17 +3778,8 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-      <c r="U68" s="3">
-        <v>0</v>
-      </c>
-      <c r="V68" s="3">
-        <v>0</v>
-      </c>
-      <c r="W68" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4326,17 +3834,8 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-      <c r="U69" s="3">
-        <v>0</v>
-      </c>
-      <c r="V69" s="3">
-        <v>0</v>
-      </c>
-      <c r="W69" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4391,17 +3890,8 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-      <c r="U70" s="3">
-        <v>0</v>
-      </c>
-      <c r="V70" s="3">
-        <v>0</v>
-      </c>
-      <c r="W70" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4456,17 +3946,8 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-      <c r="U71" s="3">
-        <v>0</v>
-      </c>
-      <c r="V71" s="3">
-        <v>0</v>
-      </c>
-      <c r="W71" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -4521,17 +4002,8 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4586,17 +4058,8 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-      <c r="U73" s="3">
-        <v>0</v>
-      </c>
-      <c r="V73" s="3">
-        <v>0</v>
-      </c>
-      <c r="W73" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4651,17 +4114,8 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-      <c r="U74" s="3">
-        <v>0</v>
-      </c>
-      <c r="V74" s="3">
-        <v>0</v>
-      </c>
-      <c r="W74" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4716,17 +4170,8 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-      <c r="U75" s="3">
-        <v>0</v>
-      </c>
-      <c r="V75" s="3">
-        <v>0</v>
-      </c>
-      <c r="W75" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -4781,17 +4226,8 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4846,22 +4282,13 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-      <c r="U77" s="3">
-        <v>0</v>
-      </c>
-      <c r="V77" s="3">
-        <v>0</v>
-      </c>
-      <c r="W77" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
@@ -4916,17 +4343,8 @@
       <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4981,17 +4399,8 @@
       <c r="T81" s="3">
         <v>-116400</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5012,11 +4421,8 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-      <c r="U82" s="3"/>
-      <c r="V82" s="3"/>
-      <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5071,17 +4477,8 @@
       <c r="T83" s="3">
         <v>4700</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
-      </c>
-      <c r="V83" s="3">
-        <v>0</v>
-      </c>
-      <c r="W83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5136,17 +4533,8 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-      <c r="U84" s="3">
-        <v>0</v>
-      </c>
-      <c r="V84" s="3">
-        <v>0</v>
-      </c>
-      <c r="W84" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5201,17 +4589,8 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-      <c r="U85" s="3">
-        <v>0</v>
-      </c>
-      <c r="V85" s="3">
-        <v>0</v>
-      </c>
-      <c r="W85" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5266,17 +4645,8 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-      <c r="U86" s="3">
-        <v>0</v>
-      </c>
-      <c r="V86" s="3">
-        <v>0</v>
-      </c>
-      <c r="W86" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5331,17 +4701,8 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-      <c r="U87" s="3">
-        <v>0</v>
-      </c>
-      <c r="V87" s="3">
-        <v>0</v>
-      </c>
-      <c r="W87" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5396,17 +4757,8 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-      <c r="U88" s="3">
-        <v>0</v>
-      </c>
-      <c r="V88" s="3">
-        <v>0</v>
-      </c>
-      <c r="W88" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5461,17 +4813,8 @@
       <c r="T89" s="3">
         <v>272800</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5492,11 +4835,8 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-      <c r="U90" s="3"/>
-      <c r="V90" s="3"/>
-      <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5551,17 +4891,8 @@
       <c r="T91" s="3">
         <v>-5500</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5616,17 +4947,8 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-      <c r="U92" s="3">
-        <v>0</v>
-      </c>
-      <c r="V92" s="3">
-        <v>0</v>
-      </c>
-      <c r="W92" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5681,17 +5003,8 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-      <c r="U93" s="3">
-        <v>0</v>
-      </c>
-      <c r="V93" s="3">
-        <v>0</v>
-      </c>
-      <c r="W93" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5746,17 +5059,8 @@
       <c r="T94" s="3">
         <v>65300</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5777,11 +5081,8 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-      <c r="U95" s="3"/>
-      <c r="V95" s="3"/>
-      <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5836,17 +5137,8 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5901,17 +5193,8 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-      <c r="U97" s="3">
-        <v>0</v>
-      </c>
-      <c r="V97" s="3">
-        <v>0</v>
-      </c>
-      <c r="W97" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5966,17 +5249,8 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-      <c r="U98" s="3">
-        <v>0</v>
-      </c>
-      <c r="V98" s="3">
-        <v>0</v>
-      </c>
-      <c r="W98" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6031,17 +5305,8 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-      <c r="U99" s="3">
-        <v>0</v>
-      </c>
-      <c r="V99" s="3">
-        <v>0</v>
-      </c>
-      <c r="W99" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6096,17 +5361,8 @@
       <c r="T100" s="3">
         <v>81900</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6161,17 +5417,8 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6225,15 +5472,6 @@
       </c>
       <c r="T102" s="3">
         <v>420000</v>
-      </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/AAII_Financials/Quarterly/SOFI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SOFI_QTR_FIN.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD5FA1F9-2DB2-4C73-9F93-DC8D668FEBC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="SOFI" sheetId="6" r:id="rId1"/>
@@ -23,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="92">
   <si>
     <t>SOFI</t>
   </si>
@@ -304,7 +303,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
@@ -370,9 +369,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -410,9 +409,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -447,7 +446,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -482,7 +481,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -655,153 +654,160 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>674600</v>
+      </c>
+      <c r="E8" s="3">
         <v>665900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>645200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>564300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>470000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>371600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>307400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>198000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>149500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>118400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>94800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>93600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>84100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>82500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>92100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>88100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>86100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>97300</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -856,8 +862,11 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -912,8 +921,11 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -934,8 +946,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -990,8 +1003,11 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1046,8 +1062,11 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1102,8 +1121,11 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1158,8 +1180,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1177,120 +1202,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>273700</v>
+      </c>
+      <c r="E17" s="3">
         <v>270400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>267700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>241100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>191500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>144000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>113800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>56500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>36900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>36400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>22900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>23600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>28600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>35200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>53300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>38900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>43300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>400900</v>
+      </c>
+      <c r="E18" s="3">
         <v>395500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>377500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>323200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>278500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>227600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>193600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>141500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>112600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>82000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>71900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>70000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>55500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>47300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>38900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>49200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>42800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>47200</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1311,120 +1343,127 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-385600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-301300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-326400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-590100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-327800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-263700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-232600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-215900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-208300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-191600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-181400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-99800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-220900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-223700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-126400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-91900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-134700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-153500</v>
       </c>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>65000</v>
+      </c>
+      <c r="E21" s="3">
         <v>142800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>104600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-214400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>9300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-34200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-57700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-78900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-82900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-5800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-140400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-150500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-62100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-18000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-77000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-101600</v>
       </c>
     </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1479,120 +1518,129 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E23" s="3">
         <v>94200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>51200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-266900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-49300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-36100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-38900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-74500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-95700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-109600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-109500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-29900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-165400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-176500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-87600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-42700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-92000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-106300</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E24" s="3">
         <v>6200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-4900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-99800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1647,120 +1695,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E26" s="3">
         <v>88000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>47900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-266700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-47500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-34400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-40000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-74200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-95800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-110400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-111000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-30000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-165300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-177600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-82600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-42900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>7800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-106400</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E27" s="3">
         <v>78000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>37700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-276900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-57600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-44400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-50200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-84400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-105900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-120300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-121200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-40200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-175400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-187500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-145500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-53100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-116400</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1815,8 +1872,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1871,8 +1931,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1927,8 +1990,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1983,120 +2049,129 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>385600</v>
+      </c>
+      <c r="E32" s="3">
         <v>301300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>326400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>590100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>327800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>263700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>232600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>215900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>208300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>191600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>181400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>99800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>220900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>223700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>126400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>91900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>134700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>153500</v>
       </c>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E33" s="3">
         <v>78000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>37700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-276900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-57600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-44400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-50200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-84400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-105900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-120300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-121200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-40200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-175400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-187500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-145500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-53100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-116400</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2151,125 +2226,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E35" s="3">
         <v>78000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>37700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-276900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-57600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-44400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-50200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-84400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-105900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-120300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-121200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-40200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-175400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-187500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-145500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-53100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-116400</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2290,8 +2374,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2312,53 +2397,54 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2334600</v>
+      </c>
+      <c r="E41" s="3">
         <v>3693400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3085000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2813900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3015700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2487800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1421900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>935200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>707300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1325100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>494700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>533500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>461900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>351300</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2368,53 +2454,56 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>291300</v>
+      </c>
+      <c r="E42" s="3">
         <v>240800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>180500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>142700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>145700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>146500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>149900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>168400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>177000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>173500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>168300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>163500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>159800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>161200</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2424,8 +2513,11 @@
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2480,8 +2572,11 @@
       <c r="T43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2536,8 +2631,11 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2592,8 +2690,11 @@
       <c r="T45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2648,8 +2749,11 @@
       <c r="T46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2681,19 +2785,19 @@
         <v>0</v>
       </c>
       <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3">
         <v>19700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>20000</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
+      <c r="Q47" s="3">
+        <v>0</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
@@ -2704,53 +2808,56 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>329600</v>
+      </c>
+      <c r="E48" s="3">
         <v>315400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>306500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>295300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>285900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>274400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>267200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>264800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>257500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>243900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>227100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>217000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>208400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>199400</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2760,53 +2867,56 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1725000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1741000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1757600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1780800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2052800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2042900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2065100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2079700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2106500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2121200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1183100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1199700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1216300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1235000</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2816,8 +2926,11 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2872,8 +2985,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,8 +3044,11 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2984,8 +3103,11 @@
       <c r="T52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3040,53 +3162,56 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>32642000</v>
+      </c>
+      <c r="E54" s="3">
         <v>31305800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>30074900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>27977200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>25561400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>22453000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>19007700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>15834900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>12670900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>12246600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>9176300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8083300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7653000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7382200</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3096,8 +3221,11 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3118,8 +3246,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3140,53 +3269,54 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>535400</v>
+      </c>
+      <c r="E57" s="3">
         <v>554200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>549700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>566500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>632500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>554100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>516200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>565900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>542300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>437300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>298200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>325500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>317900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>421100</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3196,8 +3326,11 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3252,53 +3385,56 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>100800</v>
+      </c>
+      <c r="E59" s="3">
         <v>105600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>108600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>113400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>115200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>114900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>117800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>121700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>131700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>136000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>138800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>139900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>135500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>138800</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3308,8 +3444,11 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3364,53 +3503,56 @@
       <c r="T60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3107400</v>
+      </c>
+      <c r="E61" s="3">
         <v>2895400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5240800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6251600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6495700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6141100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5502900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4614300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3778000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4986700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4041700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2874100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2432500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3942300</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3420,8 +3562,11 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3476,8 +3621,11 @@
       <c r="T62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3532,8 +3680,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3588,8 +3739,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3644,53 +3798,56 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>26740500</v>
+      </c>
+      <c r="E66" s="3">
         <v>25159800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>24519900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>22603400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>19983400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>16898500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>13479200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10333500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7164300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6715900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4478600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3514400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3125200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4502200</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3700,8 +3857,11 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3722,8 +3882,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3778,8 +3939,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3834,13 +3998,16 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>320400</v>
+        <v>0</v>
       </c>
       <c r="E70" s="3">
         <v>320400</v>
@@ -3876,11 +4043,11 @@
         <v>320400</v>
       </c>
       <c r="P70" s="3">
+        <v>320400</v>
+      </c>
+      <c r="Q70" s="3">
         <v>3173700</v>
       </c>
-      <c r="Q70" s="3">
-        <v>0</v>
-      </c>
       <c r="R70" s="3">
         <v>0</v>
       </c>
@@ -3890,8 +4057,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3946,53 +4116,56 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1698800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1716200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1804300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1852200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1585500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1537900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1503500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1463500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1389300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1293500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1183100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1072100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1042100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-876700</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4002,8 +4175,11 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4058,8 +4234,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4114,8 +4293,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4170,53 +4352,56 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5901500</v>
+      </c>
+      <c r="E76" s="3">
         <v>5825600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5234600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5053400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5257700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5234100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5208100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5181000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5186200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5210300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4377300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4248500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4207400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-293600</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4226,8 +4411,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4282,125 +4470,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E81" s="3">
         <v>78000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>37700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-276900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-57600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-44400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-50200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-84400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-105900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-120300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-121200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-40200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-175400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-187500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-145500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-53100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-116400</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4421,64 +4618,68 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>49600</v>
+      </c>
+      <c r="E83" s="3">
         <v>48500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>53400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>52500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>50100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>45300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>42400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>40300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>38100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>30700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>26500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>24100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>25000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>26000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>25500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>24700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>15000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4533,8 +4734,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4589,8 +4793,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4645,8 +4852,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4701,8 +4911,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4757,64 +4970,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-484400</v>
+      </c>
+      <c r="E89" s="3">
         <v>738200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-247900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2686500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2079900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2212800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2418800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2880300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-945500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1011200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1236300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-196500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-257400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>340100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>5200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-879400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>122100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>272800</v>
       </c>
     </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4835,64 +5054,68 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-39500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-34100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-36600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-30400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-27600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-26500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-27800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-25900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-24900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-25100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-13800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-11600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-19400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-6900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-8800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4947,8 +5170,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5003,64 +5229,70 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2194900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1261200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1413500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-168500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-267700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-40200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-51400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-50000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-54800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>49900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>30700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-159800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>58400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>180900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>70700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>90800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>32100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>65300</v>
       </c>
     </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5081,8 +5313,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5137,8 +5370,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5193,8 +5429,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5249,8 +5488,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5305,111 +5547,117 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1263100</v>
+      </c>
+      <c r="E100" s="3">
         <v>1055400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1979600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2650800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2870800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3384400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3054800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3192500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>297100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1895200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1119700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>441900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>269200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1145800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>462700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>677500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-368300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>81900</v>
       </c>
     </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-300</v>
-      </c>
-      <c r="I101" s="3">
-        <v>300</v>
       </c>
       <c r="J101" s="3">
         <v>300</v>
       </c>
       <c r="K101" s="3">
+        <v>300</v>
+      </c>
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="N101" s="3">
         <v>200</v>
       </c>
       <c r="O101" s="3">
+        <v>200</v>
+      </c>
+      <c r="P101" s="3">
         <v>-300</v>
-      </c>
-      <c r="P101" s="3">
-        <v>-100</v>
       </c>
       <c r="Q101" s="3">
         <v>-100</v>
       </c>
       <c r="R101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S101" s="3">
         <v>0</v>
@@ -5417,60 +5665,66 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1416300</v>
+      </c>
+      <c r="E102" s="3">
         <v>532300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>318600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-204100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>523600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1131200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>584900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>262500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-703300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>933800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-85800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>85800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>69900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-624900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>538400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-111100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-214100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>420000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SOFI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SOFI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="92">
   <si>
     <t>SOFI</t>
   </si>
@@ -656,181 +656,188 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>674600</v>
+        <v>691100</v>
       </c>
       <c r="E8" s="3">
-        <v>665900</v>
+        <v>587000</v>
       </c>
       <c r="F8" s="3">
-        <v>645200</v>
+        <v>637800</v>
       </c>
       <c r="G8" s="3">
-        <v>564300</v>
+        <v>603300</v>
       </c>
       <c r="H8" s="3">
-        <v>470000</v>
+        <v>515400</v>
       </c>
       <c r="I8" s="3">
-        <v>371600</v>
+        <v>485400</v>
       </c>
       <c r="J8" s="3">
+        <v>463800</v>
+      </c>
+      <c r="K8" s="3">
         <v>307400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>198000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>149500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>118400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>94800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>93600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>84100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>82500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>92100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>88100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>86100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>97300</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>123700</v>
+      </c>
+      <c r="E9" s="3">
+        <v>109700</v>
+      </c>
+      <c r="F9" s="3">
+        <v>100100</v>
+      </c>
+      <c r="G9" s="3">
+        <v>103900</v>
+      </c>
+      <c r="H9" s="3">
+        <v>98300</v>
+      </c>
+      <c r="I9" s="3">
+        <v>93900</v>
+      </c>
+      <c r="J9" s="3">
+        <v>83900</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -865,31 +872,34 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>567400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>477300</v>
+      </c>
+      <c r="F10" s="3">
+        <v>537800</v>
+      </c>
+      <c r="G10" s="3">
+        <v>499400</v>
+      </c>
+      <c r="H10" s="3">
+        <v>417100</v>
+      </c>
+      <c r="I10" s="3">
+        <v>391500</v>
+      </c>
+      <c r="J10" s="3">
+        <v>379800</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -924,8 +934,11 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -947,31 +960,32 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
+      <c r="D12" s="3">
+        <v>139700</v>
+      </c>
+      <c r="E12" s="3">
+        <v>132200</v>
+      </c>
+      <c r="F12" s="3">
+        <v>130900</v>
+      </c>
+      <c r="G12" s="3">
+        <v>146100</v>
+      </c>
+      <c r="H12" s="3">
+        <v>125700</v>
+      </c>
+      <c r="I12" s="3">
+        <v>126800</v>
+      </c>
+      <c r="J12" s="3">
+        <v>117100</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
@@ -1006,8 +1020,11 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1065,31 +1082,34 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+        <v>600</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>247200</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1124,31 +1144,34 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>51800</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>49600</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>48500</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>49200</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>52500</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>50100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>45300</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1183,8 +1206,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1203,126 +1229,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>273700</v>
+        <v>627300</v>
       </c>
       <c r="E17" s="3">
-        <v>270400</v>
+        <v>571000</v>
       </c>
       <c r="F17" s="3">
-        <v>267700</v>
+        <v>543600</v>
       </c>
       <c r="G17" s="3">
-        <v>241100</v>
+        <v>552200</v>
       </c>
       <c r="H17" s="3">
-        <v>191500</v>
+        <v>535100</v>
       </c>
       <c r="I17" s="3">
-        <v>144000</v>
+        <v>534600</v>
       </c>
       <c r="J17" s="3">
+        <v>499800</v>
+      </c>
+      <c r="K17" s="3">
         <v>113800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>56500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>36900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>36400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>22900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>23600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>28600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>35200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>53300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>38900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>43300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>400900</v>
+        <v>63900</v>
       </c>
       <c r="E18" s="3">
-        <v>395500</v>
+        <v>16000</v>
       </c>
       <c r="F18" s="3">
-        <v>377500</v>
+        <v>94200</v>
       </c>
       <c r="G18" s="3">
-        <v>323200</v>
+        <v>51200</v>
       </c>
       <c r="H18" s="3">
-        <v>278500</v>
+        <v>-19800</v>
       </c>
       <c r="I18" s="3">
-        <v>227600</v>
+        <v>-49200</v>
       </c>
       <c r="J18" s="3">
+        <v>-36100</v>
+      </c>
+      <c r="K18" s="3">
         <v>193600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>141500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>112600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>82000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>71900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>70000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>55500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>47300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>38900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>49200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>42800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>47200</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1344,149 +1377,156 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-385600</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-301300</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-326400</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-590100</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-327800</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-263700</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3">
         <v>-232600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-215900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-208300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-191600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-181400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-99800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-220900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-223700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-126400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-91900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-134700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-153500</v>
       </c>
     </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>65000</v>
+        <v>115600</v>
       </c>
       <c r="E21" s="3">
+        <v>65600</v>
+      </c>
+      <c r="F21" s="3">
         <v>142800</v>
       </c>
-      <c r="F21" s="3">
-        <v>104600</v>
-      </c>
       <c r="G21" s="3">
-        <v>-214400</v>
+        <v>100400</v>
       </c>
       <c r="H21" s="3">
-        <v>800</v>
+        <v>32800</v>
       </c>
       <c r="I21" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J21" s="3">
         <v>9300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-34200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-57700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-78900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-82900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-5800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-140400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-150500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-62100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-18000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-77000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-101600</v>
       </c>
     </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1521,126 +1561,135 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>63900</v>
+      </c>
+      <c r="E23" s="3">
         <v>15300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>94200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>51200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-266900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-49300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-36100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-38900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-74500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-95700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-109600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-109500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-29900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-165400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-176500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-87600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-42700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-92000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-106300</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-2100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-4900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-99800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1698,126 +1747,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>60700</v>
+      </c>
+      <c r="E26" s="3">
         <v>17400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>88000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>47900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-266700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-47500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-34400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-40000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-74200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-95800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-110400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-111000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-30000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-165300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-177600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-82600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-42900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>7800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-106400</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>60700</v>
+      </c>
+      <c r="E27" s="3">
         <v>8000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>78000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>37700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-276900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-57600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-44400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-50200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-84400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-105900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-120300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-121200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-40200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-175400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-187500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-145500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-53100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-116400</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1875,8 +1933,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1934,8 +1995,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1993,8 +2057,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2052,126 +2119,135 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>385600</v>
-      </c>
-      <c r="E32" s="3">
-        <v>301300</v>
-      </c>
-      <c r="F32" s="3">
-        <v>326400</v>
-      </c>
-      <c r="G32" s="3">
-        <v>590100</v>
-      </c>
-      <c r="H32" s="3">
-        <v>327800</v>
-      </c>
-      <c r="I32" s="3">
-        <v>263700</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3">
         <v>232600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>215900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>208300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>191600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>181400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>99800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>220900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>223700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>126400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>91900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>134700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>153500</v>
       </c>
     </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>8000</v>
+        <v>60700</v>
       </c>
       <c r="E33" s="3">
-        <v>78000</v>
+        <v>17400</v>
       </c>
       <c r="F33" s="3">
-        <v>37700</v>
+        <v>88000</v>
       </c>
       <c r="G33" s="3">
-        <v>-276900</v>
+        <v>47900</v>
       </c>
       <c r="H33" s="3">
-        <v>-57600</v>
+        <v>-266700</v>
       </c>
       <c r="I33" s="3">
-        <v>-44400</v>
+        <v>-47500</v>
       </c>
       <c r="J33" s="3">
+        <v>-34400</v>
+      </c>
+      <c r="K33" s="3">
         <v>-50200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-84400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-105900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-120300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-121200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-40200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-175400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-187500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-145500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-53100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-116400</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2229,131 +2305,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>8000</v>
+        <v>60700</v>
       </c>
       <c r="E35" s="3">
-        <v>78000</v>
+        <v>17400</v>
       </c>
       <c r="F35" s="3">
-        <v>37700</v>
+        <v>88000</v>
       </c>
       <c r="G35" s="3">
-        <v>-276900</v>
+        <v>47900</v>
       </c>
       <c r="H35" s="3">
-        <v>-57600</v>
+        <v>-266700</v>
       </c>
       <c r="I35" s="3">
-        <v>-44400</v>
+        <v>-47500</v>
       </c>
       <c r="J35" s="3">
+        <v>-34400</v>
+      </c>
+      <c r="K35" s="3">
         <v>-50200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-84400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-105900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-120300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-121200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-40200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-175400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-187500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-145500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-53100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-116400</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2375,8 +2460,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2398,56 +2484,57 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2355000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2334600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3693400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3085000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2813900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3015700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2487800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1421900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>935200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>707300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1325100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>494700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>533500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>461900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>351300</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2457,56 +2544,59 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>291300</v>
+        <v>10400</v>
       </c>
       <c r="E42" s="3">
-        <v>240800</v>
+        <v>15800</v>
       </c>
       <c r="F42" s="3">
-        <v>180500</v>
+        <v>5600</v>
       </c>
       <c r="G42" s="3">
-        <v>142700</v>
+        <v>6900</v>
       </c>
       <c r="H42" s="3">
-        <v>145700</v>
+        <v>79200</v>
       </c>
       <c r="I42" s="3">
-        <v>146500</v>
+        <v>11900</v>
       </c>
       <c r="J42" s="3">
+        <v>12200</v>
+      </c>
+      <c r="K42" s="3">
         <v>149900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>168400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>177000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>173500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>168300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>163500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>159800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>161200</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2516,31 +2606,34 @@
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>9359100</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>9435400</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>8150700</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>7731500</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
+        <v>424500</v>
       </c>
       <c r="I43" s="3">
-        <v>0</v>
+        <v>406600</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>386800</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2575,31 +2668,34 @@
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2634,31 +2730,34 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>0</v>
-      </c>
-      <c r="E45" s="3">
-        <v>0</v>
-      </c>
-      <c r="F45" s="3">
-        <v>0</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
+        <v>216000</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2693,31 +2792,34 @@
       <c r="U45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>29663700</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>28076400</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>27420700</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>26966700</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>24794600</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>22133300</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>19234600</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2752,31 +2854,34 @@
       <c r="U46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>1584600</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>1589200</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>996200</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>724900</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>670900</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>613600</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>382900</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2788,19 +2893,19 @@
         <v>0</v>
       </c>
       <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3">
         <v>19700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>20000</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
+      <c r="R47" s="3">
+        <v>0</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
@@ -2811,56 +2916,59 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>350400</v>
+      </c>
+      <c r="E48" s="3">
         <v>329600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>315400</v>
       </c>
-      <c r="F48" s="3">
-        <v>306500</v>
-      </c>
       <c r="G48" s="3">
+        <v>131100</v>
+      </c>
+      <c r="H48" s="3">
         <v>295300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>285900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>274400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>267200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>264800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>257500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>243900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>227100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>217000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>208400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>199400</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2870,56 +2978,59 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1725000</v>
+        <v>2004600</v>
       </c>
       <c r="E49" s="3">
-        <v>1741000</v>
+        <v>2016300</v>
       </c>
       <c r="F49" s="3">
-        <v>1757600</v>
+        <v>1981800</v>
       </c>
       <c r="G49" s="3">
-        <v>1780800</v>
+        <v>2113500</v>
       </c>
       <c r="H49" s="3">
-        <v>2052800</v>
+        <v>1923500</v>
       </c>
       <c r="I49" s="3">
-        <v>2042900</v>
+        <v>2198400</v>
       </c>
       <c r="J49" s="3">
+        <v>2189400</v>
+      </c>
+      <c r="K49" s="3">
         <v>2065100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2079700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2106500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2121200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1183100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1199700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1216300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1235000</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2929,8 +3040,11 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2988,8 +3102,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3047,31 +3164,34 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>776900</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>630400</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>591700</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>138700</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>292900</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
+        <v>330200</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>371600</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -3106,8 +3226,11 @@
       <c r="U52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3165,56 +3288,59 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>34380200</v>
+      </c>
+      <c r="E54" s="3">
         <v>32642000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>31305800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>30074900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>27977200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>25561400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>22453000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>19007700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>15834900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>12670900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>12246600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>9176300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8083300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>7653000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7382200</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3224,8 +3350,11 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3247,8 +3376,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3270,56 +3400,57 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>535400</v>
+        <v>24913800</v>
       </c>
       <c r="E57" s="3">
-        <v>554200</v>
+        <v>23515100</v>
       </c>
       <c r="F57" s="3">
-        <v>549700</v>
+        <v>22140100</v>
       </c>
       <c r="G57" s="3">
-        <v>566500</v>
+        <v>18714000</v>
       </c>
       <c r="H57" s="3">
-        <v>632500</v>
+        <v>16075800</v>
       </c>
       <c r="I57" s="3">
-        <v>554100</v>
+        <v>13187900</v>
       </c>
       <c r="J57" s="3">
+        <v>10622200</v>
+      </c>
+      <c r="K57" s="3">
         <v>516200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>565900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>542300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>437300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>298200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>325500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>317900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>421100</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3329,31 +3460,34 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>47800</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>5900</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>30100</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>13800</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3388,56 +3522,59 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>100800</v>
-      </c>
-      <c r="E59" s="3">
-        <v>105600</v>
-      </c>
-      <c r="F59" s="3">
-        <v>108600</v>
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G59" s="3">
-        <v>113400</v>
-      </c>
-      <c r="H59" s="3">
-        <v>115200</v>
-      </c>
-      <c r="I59" s="3">
-        <v>114900</v>
-      </c>
-      <c r="J59" s="3">
+        <v>103200</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K59" s="3">
         <v>117800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>121700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>131700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>136000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>138800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>139900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>135500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>138800</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3447,31 +3584,34 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>24961700</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>23515200</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>22146000</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>19116100</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>16089600</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>13196000</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>10633000</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -3506,56 +3646,59 @@
       <c r="U60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3107400</v>
+        <v>3281900</v>
       </c>
       <c r="E61" s="3">
-        <v>2895400</v>
+        <v>3208200</v>
       </c>
       <c r="F61" s="3">
-        <v>5240800</v>
+        <v>3001000</v>
       </c>
       <c r="G61" s="3">
-        <v>6251600</v>
+        <v>5337100</v>
       </c>
       <c r="H61" s="3">
-        <v>6495700</v>
+        <v>6364900</v>
       </c>
       <c r="I61" s="3">
-        <v>6141100</v>
+        <v>6610900</v>
       </c>
       <c r="J61" s="3">
+        <v>6256000</v>
+      </c>
+      <c r="K61" s="3">
         <v>5502900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4614300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3778000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4986700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4041700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2874100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2432500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3942300</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3565,31 +3708,34 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>7400</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>10100</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>7100</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>20600</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>143500</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>169700</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -3624,8 +3770,11 @@
       <c r="U62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3683,8 +3832,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3742,8 +3894,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3801,56 +3956,59 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>28258700</v>
+      </c>
+      <c r="E66" s="3">
         <v>26740500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>25159800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>24519900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>22603400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>19983400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>16898500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13479200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>10333500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7164300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6715900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4478600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3514400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3125200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4502200</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3860,8 +4018,11 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3883,8 +4044,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3942,8 +4104,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4001,8 +4166,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4010,7 +4178,7 @@
         <v>0</v>
       </c>
       <c r="E70" s="3">
-        <v>320400</v>
+        <v>0</v>
       </c>
       <c r="F70" s="3">
         <v>320400</v>
@@ -4046,11 +4214,11 @@
         <v>320400</v>
       </c>
       <c r="Q70" s="3">
+        <v>320400</v>
+      </c>
+      <c r="R70" s="3">
         <v>3173700</v>
       </c>
-      <c r="R70" s="3">
-        <v>0</v>
-      </c>
       <c r="S70" s="3">
         <v>0</v>
       </c>
@@ -4060,8 +4228,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4119,56 +4290,59 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1638100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1698800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1716200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1804300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1852200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1585500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1537900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1503500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1463500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1389300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1293500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1183100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1072100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1042100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-876700</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4178,8 +4352,11 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4237,8 +4414,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4296,8 +4476,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4355,56 +4538,59 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6121500</v>
+      </c>
+      <c r="E76" s="3">
         <v>5901500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5825600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5234600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5053400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5257700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5234100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5208100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5181000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5186200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5210300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4377300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4248500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4207400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-293600</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4414,8 +4600,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4473,131 +4662,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>8000</v>
+        <v>60700</v>
       </c>
       <c r="E81" s="3">
-        <v>78000</v>
+        <v>17400</v>
       </c>
       <c r="F81" s="3">
-        <v>37700</v>
+        <v>88000</v>
       </c>
       <c r="G81" s="3">
-        <v>-276900</v>
+        <v>47900</v>
       </c>
       <c r="H81" s="3">
-        <v>-57600</v>
+        <v>-266700</v>
       </c>
       <c r="I81" s="3">
-        <v>-44400</v>
+        <v>-47500</v>
       </c>
       <c r="J81" s="3">
+        <v>-34400</v>
+      </c>
+      <c r="K81" s="3">
         <v>-50200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-84400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-105900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-120300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-121200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-40200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-175400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-187500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-145500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-53100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-116400</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4619,67 +4817,71 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>49600</v>
+        <v>52500</v>
       </c>
       <c r="E83" s="3">
-        <v>48500</v>
+        <v>50100</v>
       </c>
       <c r="F83" s="3">
-        <v>53400</v>
+        <v>45300</v>
       </c>
       <c r="G83" s="3">
-        <v>52500</v>
+        <v>41600</v>
       </c>
       <c r="H83" s="3">
-        <v>50100</v>
+        <v>40300</v>
       </c>
       <c r="I83" s="3">
-        <v>45300</v>
+        <v>38100</v>
       </c>
       <c r="J83" s="3">
+        <v>30700</v>
+      </c>
+      <c r="K83" s="3">
         <v>42400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>40300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>38100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>30700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>26500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>24100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>25000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>26000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>25500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>24700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>15000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4737,8 +4939,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4796,8 +5001,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4855,8 +5063,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4914,8 +5125,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4973,67 +5187,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1173600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-484400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>738200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-247900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2686500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2079900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2212800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2418800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2880300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-945500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1011200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1236300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-196500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-257400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>340100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>5200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-879400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>122100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>272800</v>
       </c>
     </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5055,67 +5275,71 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-39500</v>
+        <v>-43300</v>
       </c>
       <c r="E91" s="3">
-        <v>-34100</v>
+        <v>-36700</v>
       </c>
       <c r="F91" s="3">
-        <v>-36600</v>
+        <v>-32000</v>
       </c>
       <c r="G91" s="3">
-        <v>-30400</v>
+        <v>-34300</v>
       </c>
       <c r="H91" s="3">
-        <v>-27600</v>
+        <v>-28000</v>
       </c>
       <c r="I91" s="3">
-        <v>-26500</v>
+        <v>-25400</v>
       </c>
       <c r="J91" s="3">
+        <v>-23700</v>
+      </c>
+      <c r="K91" s="3">
         <v>-27800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-25900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-24900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-25100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-13800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-11600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-19400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-7400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-6900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-8800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5173,8 +5397,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5232,67 +5459,73 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-84000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2194900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1261200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1413500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-168500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-267700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-40200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-51400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-50000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-54800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>49900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>30700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-159800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>58400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>180900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>70700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>90800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>32100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>65300</v>
       </c>
     </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5314,31 +5547,32 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5373,8 +5607,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5432,8 +5669,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5491,8 +5731,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5550,117 +5793,123 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1495200</v>
+      </c>
+      <c r="E100" s="3">
         <v>1263100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1055400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1979600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2650800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2870800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3384400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3054800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3192500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>297100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1895200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1119700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>441900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>269200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1145800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>462700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>677500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-368300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>81900</v>
       </c>
     </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>400</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G101" s="3">
+        <v>300</v>
+      </c>
+      <c r="H101" s="3">
+        <v>300</v>
+      </c>
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
-        <v>-200</v>
-      </c>
-      <c r="F101" s="3">
-        <v>500</v>
-      </c>
-      <c r="G101" s="3">
-        <v>100</v>
-      </c>
-      <c r="H101" s="3">
-        <v>400</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-300</v>
-      </c>
       <c r="J101" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="K101" s="3">
         <v>300</v>
       </c>
       <c r="L101" s="3">
+        <v>300</v>
+      </c>
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="O101" s="3">
         <v>200</v>
       </c>
       <c r="P101" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-300</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>-100</v>
       </c>
       <c r="R101" s="3">
         <v>-100</v>
       </c>
       <c r="S101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T101" s="3">
         <v>0</v>
@@ -5668,63 +5917,69 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>238100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1416300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>532300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>318600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-204100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>523600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1131200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>584900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>262500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-703300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>933800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-85800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>85800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>69900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-624900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>538400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-111100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-214100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>420000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SOFI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SOFI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="92">
   <si>
     <t>SOFI</t>
   </si>
@@ -656,192 +656,198 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>727200</v>
+      </c>
+      <c r="E8" s="3">
         <v>691100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>587000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>637800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>603300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>515400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>485400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>463800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>307400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>198000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>149500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>118400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>94800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>93600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>84100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>82500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>92100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>88100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>86100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>97300</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>128200</v>
+      </c>
+      <c r="E9" s="3">
         <v>123700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>109700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>100100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>103900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>98300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>93900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>83900</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
@@ -875,35 +881,38 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>599100</v>
+      </c>
+      <c r="E10" s="3">
         <v>567400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>477300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>537800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>499400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>417100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>391500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>379800</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -937,8 +946,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -961,35 +973,36 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>158600</v>
+      </c>
+      <c r="E12" s="3">
         <v>139700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>132200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>130900</v>
       </c>
-      <c r="G12" s="3">
-        <v>146100</v>
-      </c>
       <c r="H12" s="3">
+        <v>141800</v>
+      </c>
+      <c r="I12" s="3">
         <v>125700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>126800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>117100</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1023,8 +1036,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1085,34 +1101,37 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
         <v>600</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
+        <v>600</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3">
+        <v>100</v>
+      </c>
+      <c r="I14" s="3">
         <v>247200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>200</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1147,35 +1166,38 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>43900</v>
+      </c>
+      <c r="E15" s="3">
         <v>51800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>49600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>48500</v>
       </c>
-      <c r="G15" s="3">
-        <v>49200</v>
-      </c>
       <c r="H15" s="3">
+        <v>53400</v>
+      </c>
+      <c r="I15" s="3">
         <v>52500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>50100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>45300</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1209,8 +1231,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1230,132 +1255,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>666700</v>
+      </c>
+      <c r="E17" s="3">
         <v>627300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>571000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>543600</v>
       </c>
-      <c r="G17" s="3">
-        <v>552200</v>
-      </c>
       <c r="H17" s="3">
+        <v>552000</v>
+      </c>
+      <c r="I17" s="3">
         <v>535100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>534600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>499800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>113800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>56500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>36900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>36400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>22900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>23600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>28600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>35200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>53300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>38900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>43300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>60500</v>
+      </c>
+      <c r="E18" s="3">
         <v>63900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>16000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>94200</v>
       </c>
-      <c r="G18" s="3">
-        <v>51200</v>
-      </c>
       <c r="H18" s="3">
+        <v>51300</v>
+      </c>
+      <c r="I18" s="3">
         <v>-19800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-49200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-36100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>193600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>141500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>112600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>82000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>71900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>70000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>55500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>47300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>38900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>49200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>42800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>47200</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1378,8 +1410,9 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1404,106 +1437,112 @@
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3">
         <v>-232600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-215900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-208300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-191600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-181400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-99800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-220900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-223700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-126400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-91900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-134700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-153500</v>
       </c>
     </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>104400</v>
+      </c>
+      <c r="E21" s="3">
         <v>115600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>65600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>142800</v>
       </c>
-      <c r="G21" s="3">
-        <v>100400</v>
-      </c>
       <c r="H21" s="3">
+        <v>104700</v>
+      </c>
+      <c r="I21" s="3">
         <v>32800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>9300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-34200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-57700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-78900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-82900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-5800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-140400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-150500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-62100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-18000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-77000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-101600</v>
       </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1528,8 +1567,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1564,132 +1603,141 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>59900</v>
+      </c>
+      <c r="E23" s="3">
         <v>63900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>15300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>94200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>51200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-266900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-49300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-36100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-38900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-74500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-95700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-109600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-109500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-29900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-165400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-176500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-87600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-42700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-92000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-106300</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-272500</v>
+      </c>
+      <c r="E24" s="3">
         <v>3100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-2100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-1600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-4900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-99800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1750,132 +1798,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>332500</v>
+      </c>
+      <c r="E26" s="3">
         <v>60700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>17400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>88000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>47900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-266700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-47500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-34400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-40000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-74200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-95800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-110400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-111000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-30000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-165300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-177600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-82600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-42900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>7800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-106400</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>332500</v>
+      </c>
+      <c r="E27" s="3">
         <v>60700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>8000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>78000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>37700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-276900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-57600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-44400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-50200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-84400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-105900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-120300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-121200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-40200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-175400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-187500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-145500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-53100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-116400</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1936,8 +1993,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1998,8 +2058,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2060,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2122,8 +2188,11 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2148,106 +2217,112 @@
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3">
         <v>232600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>215900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>208300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>191600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>181400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>99800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>220900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>223700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>126400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>91900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>134700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>153500</v>
       </c>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>332500</v>
+      </c>
+      <c r="E33" s="3">
         <v>60700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>17400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>88000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>47900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-266700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-47500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-34400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-50200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-84400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-105900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-120300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-121200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-40200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-175400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-187500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-145500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-53100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-116400</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2308,137 +2383,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>332500</v>
+      </c>
+      <c r="E35" s="3">
         <v>60700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>17400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>88000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>47900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-266700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-47500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-34400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-50200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-84400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-105900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-120300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-121200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-40200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-175400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-187500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-145500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-53100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-116400</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2461,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2485,59 +2570,60 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2538300</v>
+      </c>
+      <c r="E41" s="3">
         <v>2355000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2334600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3693400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3085000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2813900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3015700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2487800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1421900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>935200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>707300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1325100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>494700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>533500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>461900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>351300</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2547,59 +2633,62 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>290700</v>
+      </c>
+      <c r="E42" s="3">
         <v>10400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>15800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>5600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>6900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>79200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>11900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>12200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>149900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>168400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>177000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>173500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>168300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>163500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>159800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>161200</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2609,35 +2698,38 @@
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>10431300</v>
+      </c>
+      <c r="E43" s="3">
         <v>9359100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>9435400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8150700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7731500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>424500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>406600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>386800</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
       <c r="L43" s="3">
         <v>0</v>
       </c>
@@ -2671,8 +2763,11 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2697,8 +2792,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2733,13 +2828,16 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>368100</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>3</v>
@@ -2747,20 +2845,20 @@
       <c r="F45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3">
         <v>216000</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
+      <c r="K45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
@@ -2795,35 +2893,38 @@
       <c r="V45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>31484400</v>
+      </c>
+      <c r="E46" s="3">
         <v>29663700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>28076400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>27420700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>26966700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>24794600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>22133300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>19234600</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2857,35 +2958,38 @@
       <c r="V46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1925200</v>
+      </c>
+      <c r="E47" s="3">
         <v>1584600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1589200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>996200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>724900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>670900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>613600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>382900</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -2896,19 +3000,19 @@
         <v>0</v>
       </c>
       <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3">
         <v>19700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>20000</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
       <c r="R47" s="3">
         <v>0</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
+      <c r="S47" s="3">
+        <v>0</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
@@ -2919,59 +3023,62 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>118900</v>
+      </c>
+      <c r="E48" s="3">
         <v>350400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>329600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>315400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>131100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>295300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>285900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>274400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>267200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>264800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>257500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>243900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>227100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>217000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>208400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>199400</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2981,59 +3088,62 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2283600</v>
+      </c>
+      <c r="E49" s="3">
         <v>2004600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2016300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1981800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2113500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1923500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2198400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2189400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2065100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2079700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2106500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2121200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1183100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1199700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1216300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1235000</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3043,8 +3153,11 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3105,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3167,35 +3283,38 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>171600</v>
+      </c>
+      <c r="E52" s="3">
         <v>776900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>630400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>591700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>138700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>292900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>330200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>371600</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
       <c r="L52" s="3">
         <v>0</v>
       </c>
@@ -3229,8 +3348,11 @@
       <c r="V52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3291,59 +3413,62 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>36251000</v>
+      </c>
+      <c r="E54" s="3">
         <v>34380200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>32642000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>31305800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>30074900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>27977200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>25561400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>22453000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>19007700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>15834900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>12670900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>12246600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>9176300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8083300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7653000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7382200</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3353,8 +3478,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3377,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3401,59 +3530,60 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>26084500</v>
+      </c>
+      <c r="E57" s="3">
         <v>24913800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>23515100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>22140100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>18714000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>16075800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>13187900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>10622200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>516200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>565900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>542300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>437300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>298200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>325500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>317900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>421100</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3463,35 +3593,38 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E58" s="3">
         <v>47800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5900</v>
       </c>
-      <c r="G58" s="3">
-        <v>30100</v>
-      </c>
       <c r="H58" s="3">
+        <v>4600</v>
+      </c>
+      <c r="I58" s="3">
         <v>13800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>8100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>10800</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -3525,13 +3658,16 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>3</v>
+      <c r="D59" s="3">
+        <v>91200</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>3</v>
@@ -3539,45 +3675,45 @@
       <c r="F59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3">
         <v>103200</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3">
         <v>117800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>121700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>131700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>136000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>138800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>139900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>135500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>138800</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3587,35 +3723,38 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>26494200</v>
+      </c>
+      <c r="E60" s="3">
         <v>24961700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>23515200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>22146000</v>
       </c>
-      <c r="G60" s="3">
-        <v>19116100</v>
-      </c>
       <c r="H60" s="3">
+        <v>19090600</v>
+      </c>
+      <c r="I60" s="3">
         <v>16089600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>13196000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10633000</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -3649,59 +3788,62 @@
       <c r="V60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3177500</v>
+      </c>
+      <c r="E61" s="3">
         <v>3281900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3208200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3001000</v>
       </c>
-      <c r="G61" s="3">
-        <v>5337100</v>
-      </c>
       <c r="H61" s="3">
+        <v>5362600</v>
+      </c>
+      <c r="I61" s="3">
         <v>6364900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6610900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6256000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5502900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4614300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3778000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4986700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4041700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2874100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2432500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3942300</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -3711,35 +3853,38 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>26500</v>
+      </c>
+      <c r="E62" s="3">
         <v>7400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>10100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>7100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>20600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>143500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>169700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1000</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -3773,8 +3918,11 @@
       <c r="V62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3835,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3897,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3959,59 +4113,62 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>29725800</v>
+      </c>
+      <c r="E66" s="3">
         <v>28258700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>26740500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>25159800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>24519900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>22603400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>19983400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>16898500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13479200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10333500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7164300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6715900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4478600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3514400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3125200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4502200</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4021,8 +4178,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4045,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4107,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4169,8 +4333,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4181,7 +4348,7 @@
         <v>0</v>
       </c>
       <c r="F70" s="3">
-        <v>320400</v>
+        <v>0</v>
       </c>
       <c r="G70" s="3">
         <v>320400</v>
@@ -4217,11 +4384,11 @@
         <v>320400</v>
       </c>
       <c r="R70" s="3">
+        <v>320400</v>
+      </c>
+      <c r="S70" s="3">
         <v>3173700</v>
       </c>
-      <c r="S70" s="3">
-        <v>0</v>
-      </c>
       <c r="T70" s="3">
         <v>0</v>
       </c>
@@ -4231,8 +4398,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4293,59 +4463,62 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1305600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1638100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1698800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1716200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1804300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1852200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1585500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1537900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1503500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1463500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1389300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1293500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1183100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1072100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1042100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-876700</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4355,8 +4528,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4417,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4479,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4541,59 +4723,62 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6525100</v>
+      </c>
+      <c r="E76" s="3">
         <v>6121500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5901500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5825600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5234600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5053400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5257700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5234100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5208100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5181000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5186200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5210300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4377300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4248500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4207400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-293600</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4603,8 +4788,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4665,137 +4853,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>332500</v>
+      </c>
+      <c r="E81" s="3">
         <v>60700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>17400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>88000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>47900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-266700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-47500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-34400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-50200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-84400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-105900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-120300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-121200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-40200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-175400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-187500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-145500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-53100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-116400</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4818,70 +5015,74 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>53400</v>
+      </c>
+      <c r="E83" s="3">
         <v>52500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>50100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>45300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>41600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>40300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>38100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>30700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>42400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>40300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>38100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>30700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>26500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>24100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>25000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>26000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>25500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>24700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>15000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4942,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5004,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5066,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5128,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5190,70 +5403,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-200100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1173600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-484400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>738200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-247900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2686500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2079900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2212800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2418800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2880300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-945500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1011200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1236300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-196500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-257400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>340100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>5200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-879400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>122100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>272800</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5276,70 +5495,74 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-42300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-43300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-36700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-32000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-34300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-28000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-25400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-23700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-27800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-25900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-24900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-25100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-13800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-11600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-19400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-7400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-6900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-8800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5400,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5462,70 +5688,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1280900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-84000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2194900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1261200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1413500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-168500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-267700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-40200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-51400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-50000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-54800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>49900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>30700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-159800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>58400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>180900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>70700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>90800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>32100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>65300</v>
       </c>
     </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5548,8 +5780,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5574,8 +5807,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -5610,8 +5843,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5672,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5734,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5796,123 +6038,129 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1220800</v>
+      </c>
+      <c r="E100" s="3">
         <v>1495200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1263100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1055400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1979600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2650800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2870800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3384400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3054800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>3192500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>297100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1895200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1119700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>441900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>269200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1145800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>462700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>677500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-368300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>81900</v>
       </c>
     </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>500</v>
+      </c>
+      <c r="E101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-300</v>
-      </c>
-      <c r="G101" s="3">
-        <v>300</v>
       </c>
       <c r="H101" s="3">
         <v>300</v>
       </c>
       <c r="I101" s="3">
+        <v>300</v>
+      </c>
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="L101" s="3">
         <v>300</v>
       </c>
       <c r="M101" s="3">
+        <v>300</v>
+      </c>
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="P101" s="3">
         <v>200</v>
       </c>
       <c r="Q101" s="3">
+        <v>200</v>
+      </c>
+      <c r="R101" s="3">
         <v>-300</v>
-      </c>
-      <c r="R101" s="3">
-        <v>-100</v>
       </c>
       <c r="S101" s="3">
         <v>-100</v>
       </c>
       <c r="T101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U101" s="3">
         <v>0</v>
@@ -5920,66 +6168,72 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-260400</v>
+      </c>
+      <c r="E102" s="3">
         <v>238100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1416300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>532300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>318600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-204100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>523600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1131200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>584900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>262500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-703300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>933800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-85800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>85800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>69900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-624900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>538400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-111100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-214100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>420000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SOFI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SOFI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="92">
   <si>
     <t>SOFI</t>
   </si>
@@ -656,201 +656,208 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>766100</v>
+      </c>
+      <c r="E8" s="3">
         <v>727200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>691100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>587000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>637800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>603300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>515400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>485400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>463800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>307400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>198000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>149500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>118400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>94800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>93600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>84100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>82500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>92100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>88100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>86100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>97300</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>135500</v>
+      </c>
+      <c r="E9" s="3">
         <v>128200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>123700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>109700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>100100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>103900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>98300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>93900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>83900</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -884,38 +891,41 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>630600</v>
+      </c>
+      <c r="E10" s="3">
         <v>599100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>567400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>477300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>537800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>499400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>417100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>391500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>379800</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -949,8 +959,11 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -974,38 +987,39 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>156200</v>
+      </c>
+      <c r="E12" s="3">
         <v>158600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>139700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>132200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>130900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>141800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>125700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>126800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>117100</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1039,8 +1053,11 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1104,37 +1121,40 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>600</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>600</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>247200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>200</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1169,38 +1189,41 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>55300</v>
+      </c>
+      <c r="E15" s="3">
         <v>43900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>51800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>49600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>48500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>53400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>52500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>50100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>45300</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1234,8 +1257,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,138 +1282,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>686300</v>
+      </c>
+      <c r="E17" s="3">
         <v>666700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>627300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>571000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>543600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>552000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>535100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>534600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>499800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>113800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>56500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>36900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>36400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>22900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>23600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>28600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>35200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>53300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>38900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>43300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>79800</v>
+      </c>
+      <c r="E18" s="3">
         <v>60500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>63900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>16000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>94200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>51300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-19800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-49200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-36100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>193600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>141500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>112600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>82000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>71900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>70000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>55500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>47300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>38900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>49200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>42800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>47200</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1411,8 +1444,9 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1440,109 +1474,115 @@
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3">
         <v>-232600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-215900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-208300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-191600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-181400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-99800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-220900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-223700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-126400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-91900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-134700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-153500</v>
       </c>
     </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>135100</v>
+      </c>
+      <c r="E21" s="3">
         <v>104400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>115600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>65600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>142800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>104700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>32800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>9300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-34200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-57700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-78900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-82900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-5800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-140400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-150500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-62100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-18000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-77000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-101600</v>
       </c>
     </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1570,8 +1610,8 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1606,138 +1646,147 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>79800</v>
+      </c>
+      <c r="E23" s="3">
         <v>59900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>63900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>15300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>94200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>51200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-266900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-49300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-36100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-38900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-74500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-95700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-109600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-109500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-29900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-165400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-176500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-87600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-42700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-92000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-106300</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E24" s="3">
         <v>-272500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-2100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-1800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-4900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-99800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1801,138 +1850,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>71100</v>
+      </c>
+      <c r="E26" s="3">
         <v>332500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>60700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>17400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>88000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>47900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-266700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-47500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-34400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-40000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-74200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-95800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-110400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-111000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-30000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-165300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-177600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-82600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-42900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>7800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-106400</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>71100</v>
+      </c>
+      <c r="E27" s="3">
         <v>332500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>60700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>8000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>78000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>37700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-276900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-57600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-44400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-50200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-84400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-105900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-120300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-121200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-40200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-175400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-187500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-145500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-53100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-116400</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1996,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2061,8 +2122,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2126,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2191,8 +2258,11 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2220,109 +2290,115 @@
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3">
         <v>232600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>215900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>208300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>191600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>181400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>99800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>220900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>223700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>126400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>91900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>134700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>153500</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>71100</v>
+      </c>
+      <c r="E33" s="3">
         <v>332500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>60700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>17400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>88000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>47900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-266700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-47500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-34400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-50200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-84400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-105900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-120300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-121200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-40200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-175400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-187500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-145500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-53100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-116400</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2386,143 +2462,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>71100</v>
+      </c>
+      <c r="E35" s="3">
         <v>332500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>60700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>17400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>88000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>47900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-266700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-47500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-34400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-50200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-84400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-105900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-120300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-121200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-40200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-175400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-187500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-145500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-53100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-116400</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2546,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2571,62 +2657,63 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2085700</v>
+      </c>
+      <c r="E41" s="3">
         <v>2538300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2355000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2334600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3693400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3085000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2813900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3015700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2487800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1421900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>935200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>707300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1325100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>494700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>533500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>461900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>351300</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2636,62 +2723,65 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E42" s="3">
         <v>290700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>10400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>15800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>5600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>6900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>79200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>11900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>12200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>149900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>168400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>177000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>173500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>168300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>163500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>159800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>161200</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2701,38 +2791,41 @@
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>10934200</v>
+      </c>
+      <c r="E43" s="3">
         <v>10431300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>9359100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9435400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8150700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7731500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>424500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>406600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>386800</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
       <c r="M43" s="3">
         <v>0</v>
       </c>
@@ -2766,8 +2859,11 @@
       <c r="W43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2795,8 +2891,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2831,37 +2927,40 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3">
         <v>368100</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3">
         <v>216000</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
+      <c r="L45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M45" s="3">
         <v>0</v>
@@ -2896,38 +2995,41 @@
       <c r="W45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>31885000</v>
+      </c>
+      <c r="E46" s="3">
         <v>31484400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>29663700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>28076400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>27420700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>26966700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>24794600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>22133300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>19234600</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2961,38 +3063,41 @@
       <c r="W46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2183000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1925200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1584600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1589200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>996200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>724900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>670900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>613600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>382900</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -3003,19 +3108,19 @@
         <v>0</v>
       </c>
       <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3">
         <v>19700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>20000</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
-      </c>
       <c r="S47" s="3">
         <v>0</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
+      <c r="T47" s="3">
+        <v>0</v>
       </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
@@ -3026,62 +3131,65 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>394400</v>
+      </c>
+      <c r="E48" s="3">
         <v>118900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>350400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>329600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>315400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>131100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>295300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>285900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>274400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>267200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>264800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>257500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>243900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>227100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>217000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>208400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>199400</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3091,62 +3199,65 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2063000</v>
+      </c>
+      <c r="E49" s="3">
         <v>2283600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2004600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2016300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1981800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2113500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1923500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2198400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2189400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2065100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2079700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2106500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2121200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1183100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1199700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1216300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1235000</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3156,8 +3267,11 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3221,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3286,38 +3403,41 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1222400</v>
+      </c>
+      <c r="E52" s="3">
         <v>171600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>776900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>630400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>591700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>138700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>292900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>330200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>371600</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
       <c r="M52" s="3">
         <v>0</v>
       </c>
@@ -3351,8 +3471,11 @@
       <c r="W52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3416,62 +3539,65 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>37749300</v>
+      </c>
+      <c r="E54" s="3">
         <v>36251000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>34380200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>32642000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>31305800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>30074900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>27977200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>25561400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>22453000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>19007700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>15834900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>12670900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>12246600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>9176300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8083300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7653000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7382200</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3481,8 +3607,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3506,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3531,62 +3661,63 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>27770400</v>
+      </c>
+      <c r="E57" s="3">
         <v>26084500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>24913800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>23515100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>22140100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>18714000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>16075800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>13187900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10622200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>516200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>565900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>542300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>437300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>298200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>325500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>317900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>421100</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3596,38 +3727,41 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>142200</v>
+      </c>
+      <c r="E58" s="3">
         <v>26700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>47800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>13800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>8100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>10800</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -3661,62 +3795,65 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3">
         <v>91200</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3">
         <v>103200</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3">
         <v>117800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>121700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>131700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>136000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>138800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>139900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>135500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>138800</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3726,38 +3863,41 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>27912700</v>
+      </c>
+      <c r="E60" s="3">
         <v>26494200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>24961700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>23515200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>22146000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>19090600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>16089600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>13196000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10633000</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -3791,62 +3931,65 @@
       <c r="W60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3139900</v>
+      </c>
+      <c r="E61" s="3">
         <v>3177500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3281900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3208200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3001000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5362600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6364900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6610900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6256000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5502900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4614300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3778000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4986700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4041700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2874100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2432500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3942300</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -3856,38 +3999,41 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E62" s="3">
         <v>26500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>7400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>10100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>20600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>143500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>169700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1000</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -3921,8 +4067,11 @@
       <c r="W62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3986,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4051,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4116,62 +4271,65 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>31070800</v>
+      </c>
+      <c r="E66" s="3">
         <v>29725800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>28258700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>26740500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>25159800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>24519900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>22603400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>19983400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>16898500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13479200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10333500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7164300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6715900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4478600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3514400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3125200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4502200</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4181,8 +4339,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4206,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4271,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4336,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4351,7 +4519,7 @@
         <v>0</v>
       </c>
       <c r="G70" s="3">
-        <v>320400</v>
+        <v>0</v>
       </c>
       <c r="H70" s="3">
         <v>320400</v>
@@ -4387,11 +4555,11 @@
         <v>320400</v>
       </c>
       <c r="S70" s="3">
+        <v>320400</v>
+      </c>
+      <c r="T70" s="3">
         <v>3173700</v>
       </c>
-      <c r="T70" s="3">
-        <v>0</v>
-      </c>
       <c r="U70" s="3">
         <v>0</v>
       </c>
@@ -4401,8 +4569,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4466,62 +4637,65 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1234500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1305600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1638100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1698800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1716200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1804300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1852200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1585500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1537900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1503500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1463500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1389300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1293500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1183100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1072100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1042100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-876700</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4531,8 +4705,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4596,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4661,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4726,62 +4909,65 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6678500</v>
+      </c>
+      <c r="E76" s="3">
         <v>6525100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6121500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5901500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5825600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5234600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5053400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5257700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5234100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5208100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5181000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5186200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5210300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4377300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4248500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4207400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-293600</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4791,8 +4977,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4856,143 +5045,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>71100</v>
+      </c>
+      <c r="E81" s="3">
         <v>332500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>60700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>17400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>88000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>47900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-266700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-47500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-34400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-50200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-84400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-105900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-120300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-121200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-40200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-175400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-187500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-145500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-53100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-116400</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5016,73 +5214,77 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>48500</v>
+      </c>
+      <c r="E83" s="3">
         <v>53400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>52500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>50100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>45300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>41600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>40300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>38100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>30700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>42400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>40300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>38100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>30700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>26500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>24100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>25000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>26000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>25500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>24700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>15000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5146,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5276,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5341,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5406,73 +5620,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-200100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1173600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-484400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>738200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-247900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2686500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2079900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2212800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2418800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2880300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-945500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1011200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1236300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-196500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-257400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>340100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>5200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-879400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>122100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>272800</v>
       </c>
     </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5496,73 +5716,77 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-52600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-42300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-43300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-36700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-32000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-34300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-28000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-25400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-23700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-27800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-25900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-24900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-25100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-13800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-11600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-19400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-7400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-6900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-8800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5626,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5691,73 +5918,79 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1440200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1280900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-84000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2194900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1261200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1413500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-168500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-267700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-40200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-51400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-50000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-54800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>49900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>30700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-159800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>58400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>180900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>70700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>90800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>32100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>65300</v>
       </c>
     </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5781,8 +6014,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5810,8 +6044,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5846,8 +6080,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5911,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5976,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6041,129 +6284,135 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1425800</v>
+      </c>
+      <c r="E100" s="3">
         <v>1220800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1495200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1263100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1055400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1979600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2650800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2870800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3384400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>3054800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>3192500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>297100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1895200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1119700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>441900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>269200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1145800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>462700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>677500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-368300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>81900</v>
       </c>
     </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E101" s="3">
         <v>500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-300</v>
-      </c>
-      <c r="H101" s="3">
-        <v>300</v>
       </c>
       <c r="I101" s="3">
         <v>300</v>
       </c>
       <c r="J101" s="3">
+        <v>300</v>
+      </c>
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="M101" s="3">
         <v>300</v>
       </c>
       <c r="N101" s="3">
+        <v>300</v>
+      </c>
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Q101" s="3">
         <v>200</v>
       </c>
       <c r="R101" s="3">
+        <v>200</v>
+      </c>
+      <c r="S101" s="3">
         <v>-300</v>
-      </c>
-      <c r="S101" s="3">
-        <v>-100</v>
       </c>
       <c r="T101" s="3">
         <v>-100</v>
       </c>
       <c r="U101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V101" s="3">
         <v>0</v>
@@ -6171,69 +6420,75 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-260400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>238100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1416300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>532300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>318600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-204100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>523600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1131200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>584900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>262500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-703300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>933800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-85800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>85800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>69900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-624900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>538400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-111100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-214100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>420000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SOFI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SOFI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="92">
   <si>
     <t>SOFI</t>
   </si>
@@ -656,211 +656,218 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>844900</v>
+      </c>
+      <c r="E8" s="3">
         <v>766100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>727200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>691100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>587000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>637800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>603300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>515400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>485400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>463800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>307400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>198000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>149500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>118400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>94800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>93600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>84100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>82500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>92100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>88100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>86100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>97300</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>150400</v>
+      </c>
+      <c r="E9" s="3">
         <v>135500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>128200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>123700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>109700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>100100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>103900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>98300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>93900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>83900</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -894,41 +901,44 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>694500</v>
+      </c>
+      <c r="E10" s="3">
         <v>630600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>599100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>567400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>477300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>537800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>499400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>417100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>391500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>379800</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -962,8 +972,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -988,41 +1001,42 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>152100</v>
+      </c>
+      <c r="E12" s="3">
         <v>156200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>158600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>139700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>132200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>130900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>141800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>125700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>126800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>117100</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1056,8 +1070,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,40 +1141,43 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>600</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
-        <v>600</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>247200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>200</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1192,41 +1212,44 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>56700</v>
+      </c>
+      <c r="E15" s="3">
         <v>55300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>43900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>51800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>49600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>48500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>53400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>52500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>50100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>45300</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1260,8 +1283,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,144 +1309,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>732700</v>
+      </c>
+      <c r="E17" s="3">
         <v>686300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>666700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>627300</v>
       </c>
-      <c r="G17" s="3">
-        <v>571000</v>
-      </c>
       <c r="H17" s="3">
+        <v>571600</v>
+      </c>
+      <c r="I17" s="3">
         <v>543600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>552000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>535100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>534600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>499800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>113800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>56500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>36900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>36400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>22900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>23600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>28600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>35200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>53300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>38900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>43300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>112200</v>
+      </c>
+      <c r="E18" s="3">
         <v>79800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>60500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>63900</v>
       </c>
-      <c r="G18" s="3">
-        <v>16000</v>
-      </c>
       <c r="H18" s="3">
+        <v>15300</v>
+      </c>
+      <c r="I18" s="3">
         <v>94200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>51300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-19800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-49200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-36100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>193600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>141500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>112600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>82000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>71900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>70000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>55500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>47300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>38900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>49200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>42800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>47200</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,8 +1478,9 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1477,112 +1511,118 @@
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3">
         <v>-232600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-215900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-208300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-191600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-181400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-99800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-220900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-223700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-126400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-91900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-134700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-153500</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>168900</v>
+      </c>
+      <c r="E21" s="3">
         <v>135100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>104400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>115600</v>
       </c>
-      <c r="G21" s="3">
-        <v>65600</v>
-      </c>
       <c r="H21" s="3">
+        <v>65000</v>
+      </c>
+      <c r="I21" s="3">
         <v>142800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>104700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>32800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>9300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-34200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-57700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-78900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-82900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-5800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-140400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-150500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-62100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-18000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-77000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-101600</v>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1613,8 +1653,8 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1649,144 +1689,153 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>112200</v>
+      </c>
+      <c r="E23" s="3">
         <v>79800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>59900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>63900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>15300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>94200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>51200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-266900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-49300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-36100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-38900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-74500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-95700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-109600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-109500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-29900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-165400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-176500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-87600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-42700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-92000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-106300</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E24" s="3">
         <v>8700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-272500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-2100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-1600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-4900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-99800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,144 +1902,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>97300</v>
+      </c>
+      <c r="E26" s="3">
         <v>71100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>332500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>60700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>17400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>88000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>47900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-266700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-47500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-34400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-40000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-74200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-95800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-110400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-111000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-30000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-165300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-177600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-82600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-42900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>7800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-106400</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>97300</v>
+      </c>
+      <c r="E27" s="3">
         <v>71100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>332500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>60700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>8000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>78000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>37700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-276900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-57600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-44400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-50200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-84400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-105900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-120300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-121200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-40200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-175400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-187500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-145500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-53100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-116400</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2115,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2125,8 +2186,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2257,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,8 +2328,11 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2293,112 +2363,118 @@
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3">
         <v>232600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>215900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>208300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>191600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>181400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>99800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>220900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>223700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>126400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>91900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>134700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>153500</v>
       </c>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>97300</v>
+      </c>
+      <c r="E33" s="3">
         <v>71100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>332500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>60700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>17400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>88000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>47900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-266700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-47500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-34400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-50200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-84400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-105900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-120300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-121200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-40200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-175400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-187500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-145500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-53100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-116400</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,149 +2541,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>97300</v>
+      </c>
+      <c r="E35" s="3">
         <v>71100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>332500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>60700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>17400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>88000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>47900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-266700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-47500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-34400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-50200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-84400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-105900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-120300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-121200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-40200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-175400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-187500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-145500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-53100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-116400</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2717,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,65 +2744,66 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2122500</v>
+      </c>
+      <c r="E41" s="3">
         <v>2085700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2538300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2355000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2334600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3693400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3085000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2813900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3015700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2487800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1421900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>935200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>707300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1325100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>494700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>533500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>461900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>351300</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2726,65 +2813,68 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E42" s="3">
         <v>8600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>290700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>10400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>15800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>5600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>6900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>79200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>11900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>12200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>149900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>168400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>177000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>173500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>168300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>163500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>159800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>161200</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2794,41 +2884,44 @@
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>12225100</v>
+      </c>
+      <c r="E43" s="3">
         <v>10934200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>10431300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9359100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>9435400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8150700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7731500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>424500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>406600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>386800</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
       <c r="N43" s="3">
         <v>0</v>
       </c>
@@ -2862,8 +2955,11 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2894,8 +2990,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2930,40 +3026,43 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3">
         <v>368100</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
         <v>216000</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
+      <c r="M45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N45" s="3">
         <v>0</v>
@@ -2998,41 +3097,44 @@
       <c r="X45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>35013400</v>
+      </c>
+      <c r="E46" s="3">
         <v>31885000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>31484400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>29663700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>28076400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>27420700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>26966700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>24794600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>22133300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>19234600</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -3066,41 +3168,44 @@
       <c r="X46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2548800</v>
+      </c>
+      <c r="E47" s="3">
         <v>2183000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1925200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1584600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1589200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>996200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>724900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>670900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>613600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>382900</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
@@ -3111,19 +3216,19 @@
         <v>0</v>
       </c>
       <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3">
         <v>19700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>20000</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
-      </c>
       <c r="T47" s="3">
         <v>0</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
+      <c r="U47" s="3">
+        <v>0</v>
       </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
@@ -3134,65 +3239,68 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>432000</v>
+      </c>
+      <c r="E48" s="3">
         <v>394400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>118900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>350400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>329600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>315400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>131100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>295300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>285900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>274400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>267200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>264800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>257500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>243900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>227100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>217000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>208400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>199400</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3202,65 +3310,68 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2032000</v>
+      </c>
+      <c r="E49" s="3">
         <v>2063000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2283600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2004600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2016300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1981800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2113500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1923500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2198400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2189400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2065100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2079700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2106500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2121200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1183100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1199700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1216300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1235000</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3270,8 +3381,11 @@
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3452,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,41 +3523,44 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1084700</v>
+      </c>
+      <c r="E52" s="3">
         <v>1222400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>171600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>776900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>630400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>591700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>138700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>292900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>330200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>371600</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
       <c r="N52" s="3">
         <v>0</v>
       </c>
@@ -3474,8 +3594,11 @@
       <c r="X52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,65 +3665,68 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>41112200</v>
+      </c>
+      <c r="E54" s="3">
         <v>37749300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>36251000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>34380200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>32642000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>31305800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>30074900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>27977200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>25561400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>22453000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>19007700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>15834900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>12670900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>12246600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>9176300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8083300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7653000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7382200</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3610,8 +3736,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3765,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,65 +3792,66 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>30136400</v>
+      </c>
+      <c r="E57" s="3">
         <v>27770400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>26084500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>24913800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>23515100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>22140100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>18714000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>16075800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>13187900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10622200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>516200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>565900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>542300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>437300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>298200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>325500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>317900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>421100</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3730,41 +3861,44 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>58900</v>
+      </c>
+      <c r="E58" s="3">
         <v>142200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>26700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>47800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>13800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>8100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>10800</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -3798,65 +3932,68 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E59" s="3">
+      <c r="D59" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3">
         <v>91200</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3">
         <v>103200</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3">
         <v>117800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>121700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>131700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>136000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>138800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>139900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>135500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>138800</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3866,41 +4003,44 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>30209500</v>
+      </c>
+      <c r="E60" s="3">
         <v>27912700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>26494200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>24961700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>23515200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>22146000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>19090600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>16089600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>13196000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10633000</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -3934,65 +4074,68 @@
       <c r="X60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4034600</v>
+      </c>
+      <c r="E61" s="3">
         <v>3139900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3177500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3281900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3208200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3001000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5362600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6364900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6610900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6256000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5502900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4614300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3778000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4986700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4041700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2874100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2432500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3942300</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4002,41 +4145,44 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3">
         <v>12800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>26500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>7400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>10100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>7100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>20600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>143500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>169700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1000</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
       <c r="N62" s="3">
         <v>0</v>
       </c>
@@ -4070,8 +4216,11 @@
       <c r="X62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4287,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4358,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,65 +4429,68 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>34251600</v>
+      </c>
+      <c r="E66" s="3">
         <v>31070800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>29725800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>28258700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>26740500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>25159800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>24519900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>22603400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>19983400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>16898500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13479200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10333500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7164300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6715900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4478600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3514400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3125200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4502200</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4342,8 +4500,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4529,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4598,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4669,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4522,7 +4690,7 @@
         <v>0</v>
       </c>
       <c r="H70" s="3">
-        <v>320400</v>
+        <v>0</v>
       </c>
       <c r="I70" s="3">
         <v>320400</v>
@@ -4558,11 +4726,11 @@
         <v>320400</v>
       </c>
       <c r="T70" s="3">
+        <v>320400</v>
+      </c>
+      <c r="U70" s="3">
         <v>3173700</v>
       </c>
-      <c r="U70" s="3">
-        <v>0</v>
-      </c>
       <c r="V70" s="3">
         <v>0</v>
       </c>
@@ -4572,8 +4740,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,65 +4811,68 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1137200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1234500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1305600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1638100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1698800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1716200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1804300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1852200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1585500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1537900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1503500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1463500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1389300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1293500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1183100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1072100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1042100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-876700</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4708,8 +4882,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4953,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5024,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,65 +5095,68 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6860600</v>
+      </c>
+      <c r="E76" s="3">
         <v>6678500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6525100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6121500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5901500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5825600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5234600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5053400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5257700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5234100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5208100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5181000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5186200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5210300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4377300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4248500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4207400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-293600</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4980,8 +5166,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5237,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>97300</v>
+      </c>
+      <c r="E81" s="3">
         <v>71100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>332500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>60700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>17400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>88000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>47900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-266700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-47500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-34400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-50200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-84400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-105900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-120300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-121200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-40200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-175400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-187500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-145500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-53100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-116400</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,76 +5413,80 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>49600</v>
+      </c>
+      <c r="E83" s="3">
         <v>48500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>53400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>52500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>50100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>45300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>41600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>40300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>38100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>30700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>42400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>40300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>38100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>30700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>26500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>24100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>25000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>26000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>25500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>24700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>15000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5553,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5624,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5695,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5766,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,76 +5837,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1466900</v>
+      </c>
+      <c r="E89" s="3">
         <v>21500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-200100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1173600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-484400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>738200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-247900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2686500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2079900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2212800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2418800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2880300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-945500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1011200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1236300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-196500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-257400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>340100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>5200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-879400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>122100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>272800</v>
       </c>
     </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,76 +5937,80 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-63500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-52600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-42300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-43300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-36700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-32000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-34300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-28000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-25400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-23700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-27800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-25900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-24900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-25100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-13800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-11600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-19400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-7400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-6900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-8800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6077,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,76 +6148,82 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1722500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1440200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1280900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-84000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2194900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1261200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1413500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-168500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-267700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-40200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-51400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-50000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-54800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>49900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>30700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-159800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>58400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>180900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>70700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>90800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>32100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>65300</v>
       </c>
     </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,8 +6248,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6047,8 +6281,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -6083,8 +6317,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6388,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6459,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,135 +6530,141 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3188400</v>
+      </c>
+      <c r="E100" s="3">
         <v>1425800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1220800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1495200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1263100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1055400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1979600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2650800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2870800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>3384400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>3054800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>3192500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>297100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1895200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1119700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>441900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>269200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1145800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>462700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>677500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-368300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>81900</v>
       </c>
     </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-300</v>
-      </c>
-      <c r="I101" s="3">
-        <v>300</v>
       </c>
       <c r="J101" s="3">
         <v>300</v>
       </c>
       <c r="K101" s="3">
+        <v>300</v>
+      </c>
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="N101" s="3">
         <v>300</v>
       </c>
       <c r="O101" s="3">
+        <v>300</v>
+      </c>
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="R101" s="3">
         <v>200</v>
       </c>
       <c r="S101" s="3">
+        <v>200</v>
+      </c>
+      <c r="T101" s="3">
         <v>-300</v>
-      </c>
-      <c r="T101" s="3">
-        <v>-100</v>
       </c>
       <c r="U101" s="3">
         <v>-100</v>
       </c>
       <c r="V101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W101" s="3">
         <v>0</v>
@@ -6423,72 +6672,78 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E102" s="3">
         <v>6800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-260400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>238100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1416300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>532300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>318600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-204100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>523600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1131200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>584900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>262500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-703300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>933800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-85800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>85800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>69900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-624900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>538400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-111100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-214100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>420000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SOFI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SOFI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="92">
   <si>
     <t>SOFI</t>
   </si>
@@ -656,231 +656,237 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1019600</v>
+      </c>
+      <c r="E8" s="3">
         <v>952400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>844900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>766100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>727200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>691100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>587000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>637800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>603300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>515400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>485400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>463800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>307400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>198000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>149500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>118400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>94800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>93600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>84100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>82500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>92100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>88100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>86100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>97300</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>161600</v>
+      </c>
+      <c r="E9" s="3">
         <v>161400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>150400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>135500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>128200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>123700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>109700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>100100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>103900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>98300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>93900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>83900</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
@@ -914,47 +920,50 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>858000</v>
+      </c>
+      <c r="E10" s="3">
         <v>791000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>694500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>630600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>599100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>567400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>477300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>537800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>499400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>417100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>391500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>379800</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
@@ -988,8 +997,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1016,47 +1028,48 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>203800</v>
+      </c>
+      <c r="E12" s="3">
         <v>167100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>152100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>156200</v>
       </c>
-      <c r="G12" s="3">
-        <v>158600</v>
-      </c>
       <c r="H12" s="3">
+        <v>173700</v>
+      </c>
+      <c r="I12" s="3">
         <v>139700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>132200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>130900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>141800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>125700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>126800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>117100</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1090,8 +1103,11 @@
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1164,8 +1180,11 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1178,8 +1197,8 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>600</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -1190,20 +1209,20 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>247200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>200</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1238,47 +1257,50 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>31900</v>
+      </c>
+      <c r="E15" s="3">
         <v>59200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>56700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>55300</v>
       </c>
-      <c r="G15" s="3">
-        <v>43900</v>
-      </c>
       <c r="H15" s="3">
+        <v>28900</v>
+      </c>
+      <c r="I15" s="3">
         <v>51800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>49600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>48500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>53400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>52500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>50100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>45300</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1312,8 +1334,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1337,156 +1362,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>834300</v>
+      </c>
+      <c r="E17" s="3">
         <v>803900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>732700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>686300</v>
       </c>
-      <c r="G17" s="3">
-        <v>666700</v>
-      </c>
       <c r="H17" s="3">
+        <v>667300</v>
+      </c>
+      <c r="I17" s="3">
         <v>627300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>571600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>543600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>552000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>535100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>534600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>499800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>113800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>56500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>36900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>36400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>22900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>23600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>28600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>35200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>53300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>38900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>43300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>185300</v>
+      </c>
+      <c r="E18" s="3">
         <v>148600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>112200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>79800</v>
       </c>
-      <c r="G18" s="3">
-        <v>60500</v>
-      </c>
       <c r="H18" s="3">
+        <v>59900</v>
+      </c>
+      <c r="I18" s="3">
         <v>63900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>15300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>94200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>51300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-19800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-49200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-36100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>193600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>141500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>112600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>82000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>71900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>70000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>55500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>47300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>38900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>49200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>42800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>47200</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1513,8 +1545,9 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1551,118 +1584,124 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3">
         <v>-232600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-215900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-208300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-191600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-181400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-99800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-220900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-223700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-126400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-91900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-134700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-153500</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>217200</v>
+      </c>
+      <c r="E21" s="3">
         <v>207800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>168900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>135100</v>
       </c>
-      <c r="G21" s="3">
-        <v>104400</v>
-      </c>
       <c r="H21" s="3">
+        <v>88800</v>
+      </c>
+      <c r="I21" s="3">
         <v>115600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>65000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>142800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>104700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>32800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>9300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-34200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-57700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-78900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-82900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-5800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-140400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-150500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-62100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-18000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-77000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-101600</v>
       </c>
     </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1699,8 +1738,8 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1735,156 +1774,165 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>185300</v>
+      </c>
+      <c r="E23" s="3">
         <v>148600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>112200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>79800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>59900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>63900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>15300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>94200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>51200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-266900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-49300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-36100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-38900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-74500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-95700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-109600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-109500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-29900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-165400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-176500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-87600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-42700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-92000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-106300</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E24" s="3">
         <v>9200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>14900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>8700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-272500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-2100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>6200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-1600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-4900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-99800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1957,156 +2005,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>173500</v>
+      </c>
+      <c r="E26" s="3">
         <v>139400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>97300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>71100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>332500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>60700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>17400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>88000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>47900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-266700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-47500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-34400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-40000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-74200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-95800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-110400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-111000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-30000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-165300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-177600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-82600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-42900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>7800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-106400</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>173500</v>
+      </c>
+      <c r="E27" s="3">
         <v>139400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>97300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>71100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>332500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>60700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>8000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>78000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>37700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-276900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-57600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-44400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-50200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-84400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-105900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-120300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-121200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-40200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-175400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-187500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-145500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-53100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-116400</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2179,8 +2236,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2253,8 +2313,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2327,8 +2390,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2401,8 +2467,11 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2439,118 +2508,124 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3">
         <v>232600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>215900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>208300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>191600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>181400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>99800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>220900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>223700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>126400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>91900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>134700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>153500</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>173500</v>
+      </c>
+      <c r="E33" s="3">
         <v>139400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>97300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>71100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>332500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>60700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>17400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>88000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>47900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-266700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-47500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-34400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-50200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-84400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-105900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-120300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-121200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-40200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-175400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-187500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-145500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-53100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-116400</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2623,161 +2698,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>173500</v>
+      </c>
+      <c r="E35" s="3">
         <v>139400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>97300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>71100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>332500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>60700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>17400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>88000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>47900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-266700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-47500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-34400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-50200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-84400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-105900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-120300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-121200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-40200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-175400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-187500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-145500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-53100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-116400</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2804,8 +2888,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2832,71 +2917,72 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4929500</v>
+      </c>
+      <c r="E41" s="3">
         <v>3246400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2122500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2085700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2538300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2355000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2334600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3693400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3085000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2813900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3015700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2487800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1421900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>935200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>707300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1325100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>494700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>533500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>461900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>351300</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2906,71 +2992,74 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>72000</v>
+      </c>
+      <c r="E42" s="3">
         <v>22100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>10600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>8600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>290700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>10400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>15800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>5600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>6900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>79200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>11900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>12200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>149900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>168400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>177000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>173500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>168300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>163500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>159800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>161200</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2980,47 +3069,50 @@
       <c r="Z42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>16067800</v>
+      </c>
+      <c r="E43" s="3">
         <v>13387400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>12225100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>10934200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>10431300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>9359100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>9435400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8150700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7731500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>424500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>406600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>386800</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
       <c r="P43" s="3">
         <v>0</v>
       </c>
@@ -3054,8 +3146,11 @@
       <c r="Z43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3092,8 +3187,8 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3128,13 +3223,16 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>633400</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>3</v>
@@ -3142,32 +3240,32 @@
       <c r="F45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3">
         <v>368100</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>216000</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
+      <c r="O45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P45" s="3">
         <v>0</v>
@@ -3202,47 +3300,50 @@
       <c r="Z45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>44992700</v>
+      </c>
+      <c r="E46" s="3">
         <v>38743300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>35013400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>31885000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>31484400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>29663700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>28076400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>27420700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>26966700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>24794600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>22133300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>19234600</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -3276,47 +3377,50 @@
       <c r="Z46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2680200</v>
+      </c>
+      <c r="E47" s="3">
         <v>2687000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2548800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2183000</v>
       </c>
-      <c r="G47" s="3">
-        <v>1925200</v>
-      </c>
       <c r="H47" s="3">
+        <v>1937800</v>
+      </c>
+      <c r="I47" s="3">
         <v>1584600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1589200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>996200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>724900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>670900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>613600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>382900</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
@@ -3327,19 +3431,19 @@
         <v>0</v>
       </c>
       <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="3">
         <v>19700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>20000</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
-      </c>
       <c r="V47" s="3">
         <v>0</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
+      <c r="W47" s="3">
+        <v>0</v>
       </c>
       <c r="X47" s="3" t="s">
         <v>3</v>
@@ -3350,71 +3454,74 @@
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>129900</v>
+      </c>
+      <c r="E48" s="3">
         <v>466000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>432000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>394400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>118900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>350400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>329600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>315400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>131100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>295300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>285900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>274400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>267200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>264800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>257500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>243900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>227100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>217000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>208400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>199400</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3424,71 +3531,74 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2384100</v>
+      </c>
+      <c r="E49" s="3">
         <v>2024900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2032000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2063000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2283600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2004600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2016300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1981800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2113500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1923500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2198400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2189400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2065100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2079700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2106500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2121200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1183100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1199700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1216300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1235000</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3498,8 +3608,11 @@
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3572,8 +3685,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3646,47 +3762,50 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>224200</v>
+      </c>
+      <c r="E52" s="3">
         <v>1371200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1084700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1222400</v>
       </c>
-      <c r="G52" s="3">
-        <v>171600</v>
-      </c>
       <c r="H52" s="3">
+        <v>159000</v>
+      </c>
+      <c r="I52" s="3">
         <v>776900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>630400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>591700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>138700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>292900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>330200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>371600</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
       <c r="P52" s="3">
         <v>0</v>
       </c>
@@ -3720,8 +3839,11 @@
       <c r="Z52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3794,71 +3916,74 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>50660500</v>
+      </c>
+      <c r="E54" s="3">
         <v>45293500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>41112200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>37749300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>36251000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>34380200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>32642000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>31305800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>30074900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>27977200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>25561400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>22453000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>19007700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>15834900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>12670900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>12246600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>9176300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>8083300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7653000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7382200</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3868,8 +3993,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3896,8 +4024,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3924,71 +4053,72 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>37570100</v>
+      </c>
+      <c r="E57" s="3">
         <v>33676400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>30136400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>27770400</v>
       </c>
-      <c r="G57" s="3">
-        <v>26084500</v>
-      </c>
       <c r="H57" s="3">
+        <v>26073500</v>
+      </c>
+      <c r="I57" s="3">
         <v>24913800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>23515100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>22140100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>18714000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>16075800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>13187900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10622200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>516200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>565900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>542300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>437300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>298200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>325500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>317900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>421100</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3998,47 +4128,50 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>32400</v>
+      </c>
+      <c r="E58" s="3">
         <v>2100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>58900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>142200</v>
       </c>
-      <c r="G58" s="3">
-        <v>26700</v>
-      </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>47800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>13800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>8100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>10800</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -4072,71 +4205,74 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>155700</v>
+      </c>
+      <c r="E59" s="3">
         <v>19000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>14200</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3">
         <v>91200</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3">
         <v>103200</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3">
         <v>117800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>121700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>131700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>136000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>138800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>139900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>135500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>138800</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4146,47 +4282,50 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>38147400</v>
+      </c>
+      <c r="E60" s="3">
         <v>33697400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>30209500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>27912700</v>
       </c>
-      <c r="G60" s="3">
-        <v>26494200</v>
-      </c>
       <c r="H60" s="3">
+        <v>26456400</v>
+      </c>
+      <c r="I60" s="3">
         <v>24961700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>23515200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>22146000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>19090600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>16089600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>13196000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10633000</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -4220,71 +4359,74 @@
       <c r="Z60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1906800</v>
+      </c>
+      <c r="E61" s="3">
         <v>2807500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4034600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3139900</v>
       </c>
-      <c r="G61" s="3">
-        <v>3177500</v>
-      </c>
       <c r="H61" s="3">
+        <v>3204200</v>
+      </c>
+      <c r="I61" s="3">
         <v>3281900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3208200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3001000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5362600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6364900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6610900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6256000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5502900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4614300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3778000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4986700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4041700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2874100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2432500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3942300</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4294,47 +4436,50 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>3</v>
+      <c r="D62" s="3">
+        <v>86800</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F62" s="3">
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3">
         <v>12800</v>
       </c>
-      <c r="G62" s="3">
-        <v>26500</v>
-      </c>
       <c r="H62" s="3">
+        <v>37500</v>
+      </c>
+      <c r="I62" s="3">
         <v>7400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>10100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>20600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>143500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>169700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1000</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
       <c r="P62" s="3">
         <v>0</v>
       </c>
@@ -4368,8 +4513,11 @@
       <c r="Z62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4442,8 +4590,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4516,8 +4667,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4590,71 +4744,74 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>40171000</v>
+      </c>
+      <c r="E66" s="3">
         <v>36513500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>34251600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>31070800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>29725800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>28258700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>26740500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>25159800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>24519900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>22603400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>19983400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>16898500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>13479200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>10333500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7164300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>6715900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4478600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3514400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3125200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4502200</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4664,8 +4821,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4692,8 +4852,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4766,8 +4927,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4840,8 +5004,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4864,7 +5031,7 @@
         <v>0</v>
       </c>
       <c r="J70" s="3">
-        <v>320400</v>
+        <v>0</v>
       </c>
       <c r="K70" s="3">
         <v>320400</v>
@@ -4900,11 +5067,11 @@
         <v>320400</v>
       </c>
       <c r="V70" s="3">
+        <v>320400</v>
+      </c>
+      <c r="W70" s="3">
         <v>3173700</v>
       </c>
-      <c r="W70" s="3">
-        <v>0</v>
-      </c>
       <c r="X70" s="3">
         <v>0</v>
       </c>
@@ -4914,8 +5081,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4988,71 +5158,74 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-824300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-997800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1137200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1234500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1305600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1638100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1698800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1716200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1804300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1852200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1585500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1537900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1503500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1463500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1389300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1293500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1183100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1072100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-1042100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-876700</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5062,8 +5235,11 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5136,8 +5312,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5210,8 +5389,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5284,71 +5466,74 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10489500</v>
+      </c>
+      <c r="E76" s="3">
         <v>8780000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6860600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6678500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6525100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6121500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5901500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5825600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5234600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5053400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5257700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5234100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5208100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5181000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5186200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5210300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4377300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4248500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4207400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-293600</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5358,8 +5543,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5432,161 +5620,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>173500</v>
+      </c>
+      <c r="E81" s="3">
         <v>139400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>97300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>71100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>332500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>60700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>17400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>88000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>47900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-266700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-47500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-34400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-50200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-84400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-105900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-120300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-121200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-40200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-175400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-187500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-145500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-53100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-116400</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5613,82 +5810,86 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>28900</v>
+      </c>
+      <c r="E83" s="3">
         <v>51800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>49600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>48500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>53400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>52500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>50100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>45300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>41600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>40300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>38100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>30700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>42400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>40300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>38100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>30700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>26500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>24100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>25000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>26000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>25500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>24700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>15000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5761,8 +5962,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5835,8 +6039,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5909,8 +6116,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5983,8 +6193,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6057,82 +6270,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-991200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1305900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1466900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>21500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-200100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1173600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-484400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>738200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-247900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2686500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2079900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2212800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2418800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2880300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-945500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1011200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1236300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-196500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-257400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>340100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>5200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-879400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>122100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>272800</v>
       </c>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6159,82 +6378,86 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-66400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-60000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-63500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-52600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-42300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-43300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-36700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-32000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-34300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-28000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-25400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-23700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-27800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-25900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-24900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-25100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-13800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-11600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-19400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-7400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-6900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-8800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6307,8 +6530,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6381,82 +6607,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2097000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1459500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1722500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1440200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1280900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-84000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2194900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1261200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1413500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-168500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-267700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-40200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-51400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-50000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-54800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>49900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>30700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-159800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>58400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>180900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>70700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>90800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>32100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>65300</v>
       </c>
     </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6483,8 +6715,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6521,8 +6754,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -6557,8 +6790,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6631,8 +6867,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6705,8 +6944,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6779,147 +7021,153 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>4697800</v>
+      </c>
+      <c r="E100" s="3">
         <v>3797400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3188400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1425800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1220800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1495200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1263100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1055400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1979600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2650800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2870800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>3384400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3054800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>3192500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>297100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1895200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1119700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>441900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>269200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1145800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>462700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>677500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-368300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>81900</v>
       </c>
     </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E101" s="3">
         <v>600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-300</v>
-      </c>
-      <c r="K101" s="3">
-        <v>300</v>
       </c>
       <c r="L101" s="3">
         <v>300</v>
       </c>
       <c r="M101" s="3">
+        <v>300</v>
+      </c>
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="P101" s="3">
         <v>300</v>
       </c>
       <c r="Q101" s="3">
+        <v>300</v>
+      </c>
+      <c r="R101" s="3">
         <v>-100</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="T101" s="3">
         <v>200</v>
       </c>
       <c r="U101" s="3">
+        <v>200</v>
+      </c>
+      <c r="V101" s="3">
         <v>-300</v>
-      </c>
-      <c r="V101" s="3">
-        <v>-100</v>
       </c>
       <c r="W101" s="3">
         <v>-100</v>
       </c>
       <c r="X101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y101" s="3">
         <v>0</v>
@@ -6927,78 +7175,84 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1610300</v>
+      </c>
+      <c r="E102" s="3">
         <v>1031800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>6800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-260400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>238100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1416300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>532300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>318600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-204100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>523600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1131200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>584900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>262500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-703300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>933800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-85800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>85800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>69900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-624900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>538400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-111100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-214100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>420000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SOFI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SOFI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="92">
   <si>
     <t>SOFI</t>
   </si>
@@ -656,240 +656,247 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1091500</v>
+      </c>
+      <c r="E8" s="3">
         <v>1019600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>952400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>844900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>766100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>727200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>691100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>587000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>637800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>603300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>515400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>485400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>463800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>307400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>198000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>149500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>118400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>94800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>93600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>84100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>82500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>92100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>88100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>86100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>97300</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>171100</v>
+      </c>
+      <c r="E9" s="3">
         <v>161600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>161400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>150400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>135500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>128200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>123700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>109700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>100100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>103900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>98300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>93900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>83900</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
@@ -923,50 +930,53 @@
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>920400</v>
+      </c>
+      <c r="E10" s="3">
         <v>858000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>791000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>694500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>630600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>599100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>567400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>477300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>537800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>499400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>417100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>391500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>379800</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1000,8 +1010,11 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1029,50 +1042,51 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>187700</v>
+      </c>
+      <c r="E12" s="3">
         <v>203800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>167100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>152100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>156200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>173700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>139700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>132200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>130900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>141800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>125700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>126800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>117100</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1106,8 +1120,11 @@
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1183,8 +1200,11 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1212,20 +1232,20 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>247200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>200</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1260,50 +1280,53 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>67600</v>
+      </c>
+      <c r="E15" s="3">
         <v>31900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>59200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>56700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>55300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>28900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>51800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>49600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>48500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>53400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>52500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>50100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>45300</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1337,8 +1360,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1363,162 +1389,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>891900</v>
+      </c>
+      <c r="E17" s="3">
         <v>834300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>803900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>732700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>686300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>667300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>627300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>571600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>543600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>552000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>535100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>534600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>499800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>113800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>56500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>36900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>36400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>22900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>23600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>28600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>35200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>53300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>38900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>43300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>199600</v>
+      </c>
+      <c r="E18" s="3">
         <v>185300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>148600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>112200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>79800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>59900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>63900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>15300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>94200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>51300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-19800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-49200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-36100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>193600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>141500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>112600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>82000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>71900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>70000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>55500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>47300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>38900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>49200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>42800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>47200</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1546,8 +1579,9 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1587,121 +1621,127 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-232600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-215900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-208300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-191600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-181400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-99800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-220900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-223700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-126400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-91900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-134700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-153500</v>
       </c>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>267100</v>
+      </c>
+      <c r="E21" s="3">
         <v>217200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>207800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>168900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>135100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>88800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>115600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>65000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>142800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>104700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>32800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>9300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-34200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-57700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-78900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-82900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-5800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-140400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-150500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-62100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-18000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-77000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-101600</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1741,8 +1781,8 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1777,162 +1817,171 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>199600</v>
+      </c>
+      <c r="E23" s="3">
         <v>185300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>148600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>112200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>79800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>59900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>63900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>15300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>94200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>51200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-266900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-49300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-36100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-38900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-74500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-95700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-109600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-109500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-29900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-165400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-176500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-87600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-42700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-92000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-106300</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>32800</v>
+      </c>
+      <c r="E24" s="3">
         <v>11800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>9200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>14900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>8700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-272500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-2100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>6200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-1800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-1600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-4900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-99800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2008,162 +2057,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>166700</v>
+      </c>
+      <c r="E26" s="3">
         <v>173500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>139400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>97300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>71100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>332500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>60700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>17400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>88000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>47900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-266700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-47500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-34400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-40000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-74200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-95800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-110400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-111000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-30000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-165300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-177600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-82600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-42900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>7800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-106400</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>166700</v>
+      </c>
+      <c r="E27" s="3">
         <v>173500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>139400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>97300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>71100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>332500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>60700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>8000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>78000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>37700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-276900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-57600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-44400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-50200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-84400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-105900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-120300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-121200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-40200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-175400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-187500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-145500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-53100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-116400</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2239,8 +2297,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2316,8 +2377,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2393,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2470,8 +2537,11 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2511,121 +2581,127 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3">
         <v>232600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>215900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>208300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>191600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>181400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>99800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>220900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>223700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>126400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>91900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>134700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>153500</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>166700</v>
+      </c>
+      <c r="E33" s="3">
         <v>173500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>139400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>97300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>71100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>332500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>60700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>17400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>88000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>47900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-266700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-47500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-34400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-50200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-84400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-105900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-120300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-121200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-40200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-175400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-187500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-145500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-53100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-116400</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2701,167 +2777,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>166700</v>
+      </c>
+      <c r="E35" s="3">
         <v>173500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>139400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>97300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>71100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>332500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>60700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>17400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>88000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>47900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-266700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-47500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-34400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-50200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-84400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-105900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-120300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-121200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-40200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-175400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-187500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-145500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-53100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-116400</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2889,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2918,74 +3004,75 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3401000</v>
+      </c>
+      <c r="E41" s="3">
         <v>4929500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3246400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2122500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2085700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2538300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2355000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2334600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3693400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3085000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2813900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3015700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2487800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1421900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>935200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>707300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1325100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>494700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>533500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>461900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>351300</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2995,74 +3082,77 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>163400</v>
+      </c>
+      <c r="E42" s="3">
         <v>72000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>22100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>10600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>8600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>290700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>10400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>15800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>5600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>6900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>79200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>11900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>12200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>149900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>168400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>177000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>173500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>168300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>163500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>159800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>161200</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3072,50 +3162,53 @@
       <c r="AA42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>16780200</v>
+      </c>
+      <c r="E43" s="3">
         <v>16067800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>13387400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>12225100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>10934200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>10431300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>9359100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>9435400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8150700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7731500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>424500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>406600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>386800</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
       <c r="Q43" s="3">
         <v>0</v>
       </c>
@@ -3149,8 +3242,11 @@
       <c r="AA43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3190,8 +3286,8 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3226,49 +3322,52 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3">
         <v>633400</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3">
         <v>368100</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>216000</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
+      <c r="P45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q45" s="3">
         <v>0</v>
@@ -3303,50 +3402,53 @@
       <c r="AA45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>46159600</v>
+      </c>
+      <c r="E46" s="3">
         <v>44992700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>38743300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>35013400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>31885000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>31484400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>29663700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>28076400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>27420700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>26966700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>24794600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>22133300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>19234600</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -3380,50 +3482,53 @@
       <c r="AA46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3492600</v>
+      </c>
+      <c r="E47" s="3">
         <v>2680200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2687000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2548800</v>
       </c>
-      <c r="G47" s="3">
-        <v>2183000</v>
-      </c>
       <c r="H47" s="3">
+        <v>2298600</v>
+      </c>
+      <c r="I47" s="3">
         <v>1937800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1584600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1589200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>996200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>724900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>670900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>613600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>382900</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
       <c r="Q47" s="3">
         <v>0</v>
       </c>
@@ -3434,19 +3539,19 @@
         <v>0</v>
       </c>
       <c r="T47" s="3">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3">
         <v>19700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>20000</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
-      </c>
       <c r="W47" s="3">
         <v>0</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>3</v>
+      <c r="X47" s="3">
+        <v>0</v>
       </c>
       <c r="Y47" s="3" t="s">
         <v>3</v>
@@ -3457,74 +3562,77 @@
       <c r="AA47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>537300</v>
+      </c>
+      <c r="E48" s="3">
         <v>129900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>466000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>432000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>394400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>118900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>350400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>329600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>315400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>131100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>295300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>285900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>274400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>267200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>264800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>257500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>243900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>227100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>217000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>208400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>199400</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3534,74 +3642,77 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1976500</v>
+      </c>
+      <c r="E49" s="3">
         <v>2384100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2024900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2032000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2063000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2283600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2004600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2016300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1981800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2113500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1923500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2198400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2189400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2065100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2079700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2106500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2121200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1183100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1199700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1216300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1235000</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3611,8 +3722,11 @@
       <c r="AA49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3688,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3765,50 +3882,53 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1531300</v>
+      </c>
+      <c r="E52" s="3">
         <v>224200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1371200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1084700</v>
       </c>
-      <c r="G52" s="3">
-        <v>1222400</v>
-      </c>
       <c r="H52" s="3">
+        <v>1106800</v>
+      </c>
+      <c r="I52" s="3">
         <v>159000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>776900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>630400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>591700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>138700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>292900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>330200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>371600</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
       <c r="Q52" s="3">
         <v>0</v>
       </c>
@@ -3842,8 +3962,11 @@
       <c r="AA52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3919,74 +4042,77 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>53698300</v>
+      </c>
+      <c r="E54" s="3">
         <v>50660500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>45293500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>41112200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>37749300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>36251000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>34380200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>32642000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>31305800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>30074900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>27977200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>25561400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>22453000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>19007700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>15834900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>12670900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>12246600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>9176300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>8083300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7653000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7382200</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3996,8 +4122,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4025,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4054,74 +4184,75 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>40945000</v>
+      </c>
+      <c r="E57" s="3">
         <v>37570100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>33676400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>30136400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>27770400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>26073500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>24913800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>23515100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>22140100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>18714000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>16075800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>13187900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10622200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>516200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>565900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>542300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>437300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>298200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>325500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>317900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>421100</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4131,50 +4262,53 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>429500</v>
+      </c>
+      <c r="E58" s="3">
         <v>32400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>58900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>142200</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>47800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>13800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>8100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>10800</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -4208,74 +4342,77 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3">
         <v>155700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>19000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>14200</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3">
         <v>91200</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3">
         <v>103200</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3">
         <v>117800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>121700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>131700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>136000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>138800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>139900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>135500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>138800</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4285,50 +4422,53 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>41374500</v>
+      </c>
+      <c r="E60" s="3">
         <v>38147400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>33697400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>30209500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>27912700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>26456400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>24961700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>23515200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>22146000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>19090600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>16089600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>13196000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10633000</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
@@ -4362,74 +4502,77 @@
       <c r="AA60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1486700</v>
+      </c>
+      <c r="E61" s="3">
         <v>1906800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2807500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4034600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3139900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3204200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3281900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3208200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3001000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5362600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6364900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6610900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6256000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5502900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4614300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3778000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4986700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4041700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2874100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2432500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3942300</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4439,50 +4582,53 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E62" s="3">
         <v>86800</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G62" s="3">
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3">
         <v>12800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>37500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>7400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>10100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>20600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>143500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>169700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1000</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
       <c r="Q62" s="3">
         <v>0</v>
       </c>
@@ -4516,8 +4662,11 @@
       <c r="AA62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4593,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4670,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4747,74 +4902,77 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>42886700</v>
+      </c>
+      <c r="E66" s="3">
         <v>40171000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>36513500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>34251600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>31070800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>29725800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>28258700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>26740500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>25159800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>24519900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>22603400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>19983400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>16898500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>13479200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>10333500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>7164300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>6715900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4478600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3514400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3125200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4502200</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4824,8 +4982,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4853,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4930,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5007,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5034,7 +5202,7 @@
         <v>0</v>
       </c>
       <c r="K70" s="3">
-        <v>320400</v>
+        <v>0</v>
       </c>
       <c r="L70" s="3">
         <v>320400</v>
@@ -5070,11 +5238,11 @@
         <v>320400</v>
       </c>
       <c r="W70" s="3">
+        <v>320400</v>
+      </c>
+      <c r="X70" s="3">
         <v>3173700</v>
       </c>
-      <c r="X70" s="3">
-        <v>0</v>
-      </c>
       <c r="Y70" s="3">
         <v>0</v>
       </c>
@@ -5084,8 +5252,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5161,74 +5332,77 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-657500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-824300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-997800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1137200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1234500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1305600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1638100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1698800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1716200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1804300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1852200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1585500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1537900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1503500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1463500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1389300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1293500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1183100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-1072100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-1042100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-876700</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5238,8 +5412,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5315,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5392,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5469,74 +5652,77 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10811600</v>
+      </c>
+      <c r="E76" s="3">
         <v>10489500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8780000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6860600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6678500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6525100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6121500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5901500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5825600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5234600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5053400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5257700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5234100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5208100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5181000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5186200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>5210300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4377300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4248500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4207400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-293600</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5546,8 +5732,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5623,167 +5812,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>166700</v>
+      </c>
+      <c r="E81" s="3">
         <v>173500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>139400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>97300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>71100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>332500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>60700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>17400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>88000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>47900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-266700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-47500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-34400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-50200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-84400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-105900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-120300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-121200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-40200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-175400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-187500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-145500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-53100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-116400</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5811,85 +6009,89 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>55300</v>
+      </c>
+      <c r="E83" s="3">
         <v>28900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>51800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>49600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>48500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>53400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>52500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>50100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>45300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>41600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>40300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>38100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>30700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>42400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>40300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>38100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>30700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>26500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>24100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>25000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>26000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>25500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>24700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>15000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>4700</v>
       </c>
     </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5965,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6042,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6119,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6196,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6273,85 +6487,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2315000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-991200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1305900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1466900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>21500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-200100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1173600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-484400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>738200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-247900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2686500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2079900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2212800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2418800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2880300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-945500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1011200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1236300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-196500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-257400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>340100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>5200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-879400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>122100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>272800</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6379,85 +6599,89 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-67600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-66400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-60000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-63500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-52600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-42300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-43300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-36700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-32000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-34300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-28000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-25400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-23700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-27800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-25900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-24900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-25100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-13800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-11600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-19400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-7400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-6900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-8800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-5500</v>
       </c>
     </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6533,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6610,85 +6837,91 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2394300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2097000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1459500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1722500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1440200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1280900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-84000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2194900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1261200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1413500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-168500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-267700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-40200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-51400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-50000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-54800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>49900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>30700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-159800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>58400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>180900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>70700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>90800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>32100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>65300</v>
       </c>
     </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6716,8 +6949,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6757,8 +6991,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -6793,8 +7027,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6870,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6947,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7024,153 +7267,159 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3114600</v>
+      </c>
+      <c r="E100" s="3">
         <v>4697800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3797400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3188400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1425800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1220800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1495200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1263100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1055400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1979600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2650800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2870800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3384400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>3054800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>3192500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>297100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1895200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1119700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>441900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>269200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1145800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>462700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>677500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-368300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>81900</v>
       </c>
     </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-300</v>
-      </c>
-      <c r="L101" s="3">
-        <v>300</v>
       </c>
       <c r="M101" s="3">
         <v>300</v>
       </c>
       <c r="N101" s="3">
+        <v>300</v>
+      </c>
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="Q101" s="3">
         <v>300</v>
       </c>
       <c r="R101" s="3">
+        <v>300</v>
+      </c>
+      <c r="S101" s="3">
         <v>-100</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="U101" s="3">
         <v>200</v>
       </c>
       <c r="V101" s="3">
+        <v>200</v>
+      </c>
+      <c r="W101" s="3">
         <v>-300</v>
-      </c>
-      <c r="W101" s="3">
-        <v>-100</v>
       </c>
       <c r="X101" s="3">
         <v>-100</v>
       </c>
       <c r="Y101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Z101" s="3">
         <v>0</v>
@@ -7178,81 +7427,87 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1595500</v>
+      </c>
+      <c r="E102" s="3">
         <v>1610300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1031800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>6800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-260400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>238100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1416300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>532300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>318600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-204100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>523600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1131200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>584900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>262500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-703300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>933800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-85800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>85800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>69900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-624900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>538400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-111100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-214100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>420000</v>
       </c>
     </row>
